--- a/AAII_Financials/Yearly/RICOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RICOY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -723,25 +723,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>14171000</v>
+        <v>14384400</v>
       </c>
       <c r="E8" s="3">
-        <v>11677000</v>
+        <v>11852900</v>
       </c>
       <c r="F8" s="3">
-        <v>11168900</v>
+        <v>11337100</v>
       </c>
       <c r="G8" s="3">
-        <v>13337000</v>
+        <v>13537800</v>
       </c>
       <c r="H8" s="3">
-        <v>13367800</v>
+        <v>13569200</v>
       </c>
       <c r="I8" s="3">
-        <v>13700700</v>
+        <v>13907100</v>
       </c>
       <c r="J8" s="3">
-        <v>13471900</v>
+        <v>13674800</v>
       </c>
       <c r="K8" s="3">
         <v>16236400</v>
@@ -765,25 +765,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>9221400</v>
+        <v>9360200</v>
       </c>
       <c r="E9" s="3">
-        <v>7542500</v>
+        <v>7656100</v>
       </c>
       <c r="F9" s="3">
-        <v>7368800</v>
+        <v>7479800</v>
       </c>
       <c r="G9" s="3">
-        <v>8544100</v>
+        <v>8672800</v>
       </c>
       <c r="H9" s="3">
-        <v>8275700</v>
+        <v>8400400</v>
       </c>
       <c r="I9" s="3">
-        <v>8448500</v>
+        <v>8575700</v>
       </c>
       <c r="J9" s="3">
-        <v>8235400</v>
+        <v>8359400</v>
       </c>
       <c r="K9" s="3">
         <v>9753900</v>
@@ -807,25 +807,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>4949600</v>
+        <v>5024100</v>
       </c>
       <c r="E10" s="3">
-        <v>4134500</v>
+        <v>4196800</v>
       </c>
       <c r="F10" s="3">
-        <v>3800100</v>
+        <v>3857300</v>
       </c>
       <c r="G10" s="3">
-        <v>4792800</v>
+        <v>4865000</v>
       </c>
       <c r="H10" s="3">
-        <v>5092100</v>
+        <v>5168800</v>
       </c>
       <c r="I10" s="3">
-        <v>5252300</v>
+        <v>5331400</v>
       </c>
       <c r="J10" s="3">
-        <v>5236500</v>
+        <v>5315400</v>
       </c>
       <c r="K10" s="3">
         <v>6482400</v>
@@ -867,25 +867,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>566500</v>
+        <v>575000</v>
       </c>
       <c r="E12" s="3">
-        <v>502800</v>
+        <v>510400</v>
       </c>
       <c r="F12" s="3">
-        <v>525800</v>
+        <v>533800</v>
       </c>
       <c r="G12" s="3">
-        <v>585800</v>
+        <v>594600</v>
       </c>
       <c r="H12" s="3">
-        <v>624300</v>
+        <v>633700</v>
       </c>
       <c r="I12" s="3">
-        <v>624100</v>
+        <v>633500</v>
       </c>
       <c r="J12" s="3">
-        <v>666600</v>
+        <v>676600</v>
       </c>
       <c r="K12" s="3">
         <v>750000</v>
@@ -951,22 +951,22 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-4700</v>
+        <v>-4800</v>
       </c>
       <c r="E14" s="3">
-        <v>13400</v>
+        <v>13600</v>
       </c>
       <c r="F14" s="3">
-        <v>330500</v>
+        <v>335500</v>
       </c>
       <c r="G14" s="3">
-        <v>74800</v>
+        <v>75900</v>
       </c>
       <c r="H14" s="3">
-        <v>142200</v>
+        <v>144400</v>
       </c>
       <c r="I14" s="3">
-        <v>1339400</v>
+        <v>1359600</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>10</v>
@@ -993,25 +993,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>376700</v>
+        <v>382400</v>
       </c>
       <c r="E15" s="3">
-        <v>334200</v>
+        <v>339300</v>
       </c>
       <c r="F15" s="3">
-        <v>361400</v>
+        <v>366800</v>
       </c>
       <c r="G15" s="3">
-        <v>354100</v>
+        <v>359500</v>
       </c>
       <c r="H15" s="3">
-        <v>165100</v>
+        <v>167600</v>
       </c>
       <c r="I15" s="3">
-        <v>266200</v>
+        <v>270200</v>
       </c>
       <c r="J15" s="3">
-        <v>267500</v>
+        <v>271500</v>
       </c>
       <c r="K15" s="3">
         <v>273000</v>
@@ -1050,25 +1050,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>13648100</v>
+        <v>13853700</v>
       </c>
       <c r="E17" s="3">
-        <v>11411100</v>
+        <v>11582900</v>
       </c>
       <c r="F17" s="3">
-        <v>11470600</v>
+        <v>11643300</v>
       </c>
       <c r="G17" s="3">
-        <v>12812100</v>
+        <v>13005100</v>
       </c>
       <c r="H17" s="3">
-        <v>12791200</v>
+        <v>12983900</v>
       </c>
       <c r="I17" s="3">
-        <v>14468800</v>
+        <v>14686700</v>
       </c>
       <c r="J17" s="3">
-        <v>13246900</v>
+        <v>13446400</v>
       </c>
       <c r="K17" s="3">
         <v>15484500</v>
@@ -1092,25 +1092,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>522800</v>
+        <v>530700</v>
       </c>
       <c r="E18" s="3">
-        <v>265900</v>
+        <v>270000</v>
       </c>
       <c r="F18" s="3">
-        <v>-301600</v>
+        <v>-306200</v>
       </c>
       <c r="G18" s="3">
-        <v>524800</v>
+        <v>532700</v>
       </c>
       <c r="H18" s="3">
-        <v>576600</v>
+        <v>585300</v>
       </c>
       <c r="I18" s="3">
-        <v>-768100</v>
+        <v>-779700</v>
       </c>
       <c r="J18" s="3">
-        <v>225000</v>
+        <v>228400</v>
       </c>
       <c r="K18" s="3">
         <v>751900</v>
@@ -1152,25 +1152,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>57000</v>
+        <v>57800</v>
       </c>
       <c r="E20" s="3">
-        <v>50400</v>
+        <v>51200</v>
       </c>
       <c r="F20" s="3">
-        <v>49400</v>
+        <v>50200</v>
       </c>
       <c r="G20" s="3">
-        <v>17400</v>
+        <v>17700</v>
       </c>
       <c r="H20" s="3">
-        <v>20500</v>
+        <v>20800</v>
       </c>
       <c r="I20" s="3">
-        <v>-11800</v>
+        <v>-12000</v>
       </c>
       <c r="J20" s="3">
-        <v>24100</v>
+        <v>24400</v>
       </c>
       <c r="K20" s="3">
         <v>-500</v>
@@ -1194,25 +1194,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1224100</v>
+        <v>1248400</v>
       </c>
       <c r="E21" s="3">
-        <v>914400</v>
+        <v>933700</v>
       </c>
       <c r="F21" s="3">
-        <v>439300</v>
+        <v>452200</v>
       </c>
       <c r="G21" s="3">
-        <v>1340000</v>
+        <v>1367500</v>
       </c>
       <c r="H21" s="3">
-        <v>1220400</v>
+        <v>1244400</v>
       </c>
       <c r="I21" s="3">
-        <v>-63900</v>
+        <v>-58300</v>
       </c>
       <c r="J21" s="3">
-        <v>955600</v>
+        <v>976400</v>
       </c>
       <c r="K21" s="3">
         <v>1533000</v>
@@ -1236,25 +1236,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>39900</v>
+        <v>40500</v>
       </c>
       <c r="E22" s="3">
-        <v>21600</v>
+        <v>22000</v>
       </c>
       <c r="F22" s="3">
-        <v>20200</v>
+        <v>20500</v>
       </c>
       <c r="G22" s="3">
-        <v>38300</v>
+        <v>38900</v>
       </c>
       <c r="H22" s="3">
-        <v>39600</v>
+        <v>40200</v>
       </c>
       <c r="I22" s="3">
-        <v>44700</v>
+        <v>45300</v>
       </c>
       <c r="J22" s="3">
-        <v>50100</v>
+        <v>50900</v>
       </c>
       <c r="K22" s="3">
         <v>48100</v>
@@ -1278,25 +1278,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>539900</v>
+        <v>548000</v>
       </c>
       <c r="E23" s="3">
-        <v>294700</v>
+        <v>299200</v>
       </c>
       <c r="F23" s="3">
-        <v>-272400</v>
+        <v>-276500</v>
       </c>
       <c r="G23" s="3">
-        <v>503900</v>
+        <v>511500</v>
       </c>
       <c r="H23" s="3">
-        <v>557500</v>
+        <v>565900</v>
       </c>
       <c r="I23" s="3">
-        <v>-824600</v>
+        <v>-837000</v>
       </c>
       <c r="J23" s="3">
-        <v>198900</v>
+        <v>201900</v>
       </c>
       <c r="K23" s="3">
         <v>703300</v>
@@ -1320,25 +1320,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>170400</v>
+        <v>173000</v>
       </c>
       <c r="E24" s="3">
-        <v>91400</v>
+        <v>92800</v>
       </c>
       <c r="F24" s="3">
-        <v>-55500</v>
+        <v>-56400</v>
       </c>
       <c r="G24" s="3">
-        <v>209000</v>
+        <v>212200</v>
       </c>
       <c r="H24" s="3">
-        <v>189800</v>
+        <v>192700</v>
       </c>
       <c r="I24" s="3">
-        <v>27500</v>
+        <v>27900</v>
       </c>
       <c r="J24" s="3">
-        <v>136200</v>
+        <v>138300</v>
       </c>
       <c r="K24" s="3">
         <v>208600</v>
@@ -1404,25 +1404,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>369500</v>
+        <v>375000</v>
       </c>
       <c r="E26" s="3">
-        <v>203400</v>
+        <v>206400</v>
       </c>
       <c r="F26" s="3">
-        <v>-216900</v>
+        <v>-220200</v>
       </c>
       <c r="G26" s="3">
-        <v>294900</v>
+        <v>299300</v>
       </c>
       <c r="H26" s="3">
-        <v>367700</v>
+        <v>373200</v>
       </c>
       <c r="I26" s="3">
-        <v>-852100</v>
+        <v>-864900</v>
       </c>
       <c r="J26" s="3">
-        <v>62700</v>
+        <v>63600</v>
       </c>
       <c r="K26" s="3">
         <v>494700</v>
@@ -1446,25 +1446,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>361000</v>
+        <v>366400</v>
       </c>
       <c r="E27" s="3">
-        <v>201700</v>
+        <v>204700</v>
       </c>
       <c r="F27" s="3">
-        <v>-217300</v>
+        <v>-220600</v>
       </c>
       <c r="G27" s="3">
-        <v>262600</v>
+        <v>266500</v>
       </c>
       <c r="H27" s="3">
-        <v>328900</v>
+        <v>333800</v>
       </c>
       <c r="I27" s="3">
-        <v>-890200</v>
+        <v>-903600</v>
       </c>
       <c r="J27" s="3">
-        <v>23200</v>
+        <v>23500</v>
       </c>
       <c r="K27" s="3">
         <v>462900</v>
@@ -1545,7 +1545,7 @@
         <v>10</v>
       </c>
       <c r="I29" s="3">
-        <v>-8700</v>
+        <v>-8800</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>10</v>
@@ -1656,25 +1656,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-57000</v>
+        <v>-57800</v>
       </c>
       <c r="E32" s="3">
-        <v>-50400</v>
+        <v>-51200</v>
       </c>
       <c r="F32" s="3">
-        <v>-49400</v>
+        <v>-50200</v>
       </c>
       <c r="G32" s="3">
-        <v>-17400</v>
+        <v>-17700</v>
       </c>
       <c r="H32" s="3">
-        <v>-20500</v>
+        <v>-20800</v>
       </c>
       <c r="I32" s="3">
-        <v>11800</v>
+        <v>12000</v>
       </c>
       <c r="J32" s="3">
-        <v>-24100</v>
+        <v>-24400</v>
       </c>
       <c r="K32" s="3">
         <v>500</v>
@@ -1698,25 +1698,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>361000</v>
+        <v>366400</v>
       </c>
       <c r="E33" s="3">
-        <v>201700</v>
+        <v>204700</v>
       </c>
       <c r="F33" s="3">
-        <v>-217300</v>
+        <v>-220600</v>
       </c>
       <c r="G33" s="3">
-        <v>262600</v>
+        <v>266500</v>
       </c>
       <c r="H33" s="3">
-        <v>328900</v>
+        <v>333800</v>
       </c>
       <c r="I33" s="3">
-        <v>-898900</v>
+        <v>-912400</v>
       </c>
       <c r="J33" s="3">
-        <v>23200</v>
+        <v>23500</v>
       </c>
       <c r="K33" s="3">
         <v>462900</v>
@@ -1782,25 +1782,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>361000</v>
+        <v>366400</v>
       </c>
       <c r="E35" s="3">
-        <v>201700</v>
+        <v>204700</v>
       </c>
       <c r="F35" s="3">
-        <v>-217300</v>
+        <v>-220600</v>
       </c>
       <c r="G35" s="3">
-        <v>262600</v>
+        <v>266500</v>
       </c>
       <c r="H35" s="3">
-        <v>328900</v>
+        <v>333800</v>
       </c>
       <c r="I35" s="3">
-        <v>-898900</v>
+        <v>-912400</v>
       </c>
       <c r="J35" s="3">
-        <v>23200</v>
+        <v>23500</v>
       </c>
       <c r="K35" s="3">
         <v>462900</v>
@@ -1907,25 +1907,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1473300</v>
+        <v>1495500</v>
       </c>
       <c r="E41" s="3">
-        <v>1595600</v>
+        <v>1619700</v>
       </c>
       <c r="F41" s="3">
-        <v>2223100</v>
+        <v>2256600</v>
       </c>
       <c r="G41" s="3">
-        <v>1745200</v>
+        <v>1771500</v>
       </c>
       <c r="H41" s="3">
-        <v>1594300</v>
+        <v>1618300</v>
       </c>
       <c r="I41" s="3">
-        <v>1066200</v>
+        <v>1082200</v>
       </c>
       <c r="J41" s="3">
-        <v>839500</v>
+        <v>852100</v>
       </c>
       <c r="K41" s="3">
         <v>1238600</v>
@@ -1949,25 +1949,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>624900</v>
+        <v>634300</v>
       </c>
       <c r="E42" s="3">
-        <v>613400</v>
+        <v>622600</v>
       </c>
       <c r="F42" s="3">
-        <v>617900</v>
+        <v>627200</v>
       </c>
       <c r="G42" s="3">
-        <v>579500</v>
+        <v>588200</v>
       </c>
       <c r="H42" s="3">
-        <v>1955000</v>
+        <v>1984400</v>
       </c>
       <c r="I42" s="3">
-        <v>2305000</v>
+        <v>2339700</v>
       </c>
       <c r="J42" s="3">
-        <v>1894000</v>
+        <v>1922500</v>
       </c>
       <c r="K42" s="3">
         <v>2001800</v>
@@ -1991,25 +1991,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3163500</v>
+        <v>3211100</v>
       </c>
       <c r="E43" s="3">
-        <v>2637100</v>
+        <v>2676800</v>
       </c>
       <c r="F43" s="3">
-        <v>2603800</v>
+        <v>2643000</v>
       </c>
       <c r="G43" s="3">
-        <v>2608100</v>
+        <v>2647300</v>
       </c>
       <c r="H43" s="3">
-        <v>4015900</v>
+        <v>4076400</v>
       </c>
       <c r="I43" s="3">
-        <v>3915900</v>
+        <v>3974900</v>
       </c>
       <c r="J43" s="3">
-        <v>3760300</v>
+        <v>3817000</v>
       </c>
       <c r="K43" s="3">
         <v>4146900</v>
@@ -2033,25 +2033,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>2087400</v>
+        <v>2118800</v>
       </c>
       <c r="E44" s="3">
-        <v>1544200</v>
+        <v>1567400</v>
       </c>
       <c r="F44" s="3">
-        <v>1275000</v>
+        <v>1294200</v>
       </c>
       <c r="G44" s="3">
-        <v>1336300</v>
+        <v>1356400</v>
       </c>
       <c r="H44" s="3">
-        <v>1379400</v>
+        <v>1400200</v>
       </c>
       <c r="I44" s="3">
-        <v>1198400</v>
+        <v>1216500</v>
       </c>
       <c r="J44" s="3">
-        <v>1344900</v>
+        <v>1365200</v>
       </c>
       <c r="K44" s="3">
         <v>1522100</v>
@@ -2075,25 +2075,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>454800</v>
+        <v>461700</v>
       </c>
       <c r="E45" s="3">
-        <v>332200</v>
+        <v>337200</v>
       </c>
       <c r="F45" s="3">
-        <v>310300</v>
+        <v>314900</v>
       </c>
       <c r="G45" s="3">
-        <v>7715700</v>
+        <v>7831900</v>
       </c>
       <c r="H45" s="3">
-        <v>283500</v>
+        <v>287700</v>
       </c>
       <c r="I45" s="3">
-        <v>332300</v>
+        <v>337400</v>
       </c>
       <c r="J45" s="3">
-        <v>389600</v>
+        <v>395500</v>
       </c>
       <c r="K45" s="3">
         <v>448600</v>
@@ -2117,25 +2117,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>7804000</v>
+        <v>7921500</v>
       </c>
       <c r="E46" s="3">
-        <v>6722500</v>
+        <v>6823700</v>
       </c>
       <c r="F46" s="3">
-        <v>7030100</v>
+        <v>7135900</v>
       </c>
       <c r="G46" s="3">
-        <v>13984800</v>
+        <v>14195400</v>
       </c>
       <c r="H46" s="3">
-        <v>9228000</v>
+        <v>9367000</v>
       </c>
       <c r="I46" s="3">
-        <v>8817800</v>
+        <v>8950600</v>
       </c>
       <c r="J46" s="3">
-        <v>8228400</v>
+        <v>8352300</v>
       </c>
       <c r="K46" s="3">
         <v>9358000</v>
@@ -2159,25 +2159,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1580600</v>
+        <v>1604400</v>
       </c>
       <c r="E47" s="3">
-        <v>1474400</v>
+        <v>1496600</v>
       </c>
       <c r="F47" s="3">
-        <v>1554400</v>
+        <v>1577800</v>
       </c>
       <c r="G47" s="3">
-        <v>1118400</v>
+        <v>1135300</v>
       </c>
       <c r="H47" s="3">
-        <v>4935200</v>
+        <v>5009600</v>
       </c>
       <c r="I47" s="3">
-        <v>4782900</v>
+        <v>4854900</v>
       </c>
       <c r="J47" s="3">
-        <v>4898600</v>
+        <v>4972400</v>
       </c>
       <c r="K47" s="3">
         <v>5058200</v>
@@ -2201,25 +2201,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1683300</v>
+        <v>1708700</v>
       </c>
       <c r="E48" s="3">
-        <v>1634600</v>
+        <v>1659200</v>
       </c>
       <c r="F48" s="3">
-        <v>1697300</v>
+        <v>1722900</v>
       </c>
       <c r="G48" s="3">
-        <v>1733000</v>
+        <v>1759100</v>
       </c>
       <c r="H48" s="3">
-        <v>1661900</v>
+        <v>1686900</v>
       </c>
       <c r="I48" s="3">
-        <v>1660000</v>
+        <v>1685000</v>
       </c>
       <c r="J48" s="3">
-        <v>1801100</v>
+        <v>1828300</v>
       </c>
       <c r="K48" s="3">
         <v>2032600</v>
@@ -2243,25 +2243,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2432900</v>
+        <v>2469500</v>
       </c>
       <c r="E49" s="3">
-        <v>1723000</v>
+        <v>1748900</v>
       </c>
       <c r="F49" s="3">
-        <v>1497400</v>
+        <v>1519900</v>
       </c>
       <c r="G49" s="3">
-        <v>1539800</v>
+        <v>1563000</v>
       </c>
       <c r="H49" s="3">
-        <v>1459500</v>
+        <v>1481500</v>
       </c>
       <c r="I49" s="3">
-        <v>1441700</v>
+        <v>1463500</v>
       </c>
       <c r="J49" s="3">
-        <v>2577500</v>
+        <v>2616300</v>
       </c>
       <c r="K49" s="3">
         <v>3041700</v>
@@ -2369,25 +2369,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>774900</v>
+        <v>786600</v>
       </c>
       <c r="E52" s="3">
-        <v>751200</v>
+        <v>762500</v>
       </c>
       <c r="F52" s="3">
-        <v>756300</v>
+        <v>767700</v>
       </c>
       <c r="G52" s="3">
-        <v>665100</v>
+        <v>675100</v>
       </c>
       <c r="H52" s="3">
-        <v>810200</v>
+        <v>822400</v>
       </c>
       <c r="I52" s="3">
-        <v>834000</v>
+        <v>846500</v>
       </c>
       <c r="J52" s="3">
-        <v>816000</v>
+        <v>828300</v>
       </c>
       <c r="K52" s="3">
         <v>916500</v>
@@ -2453,25 +2453,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>14275700</v>
+        <v>14490700</v>
       </c>
       <c r="E54" s="3">
-        <v>12305600</v>
+        <v>12490900</v>
       </c>
       <c r="F54" s="3">
-        <v>12535400</v>
+        <v>12724200</v>
       </c>
       <c r="G54" s="3">
-        <v>19041200</v>
+        <v>19327900</v>
       </c>
       <c r="H54" s="3">
-        <v>18094900</v>
+        <v>18367400</v>
       </c>
       <c r="I54" s="3">
-        <v>17536400</v>
+        <v>17800500</v>
       </c>
       <c r="J54" s="3">
-        <v>18321700</v>
+        <v>18597600</v>
       </c>
       <c r="K54" s="3">
         <v>20407000</v>
@@ -2531,25 +2531,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1448100</v>
+        <v>1469900</v>
       </c>
       <c r="E57" s="3">
-        <v>1177800</v>
+        <v>1195500</v>
       </c>
       <c r="F57" s="3">
-        <v>1335900</v>
+        <v>1356100</v>
       </c>
       <c r="G57" s="3">
-        <v>1191400</v>
+        <v>1209400</v>
       </c>
       <c r="H57" s="3">
-        <v>1382700</v>
+        <v>1403500</v>
       </c>
       <c r="I57" s="3">
-        <v>1290900</v>
+        <v>1310300</v>
       </c>
       <c r="J57" s="3">
-        <v>1296300</v>
+        <v>1315800</v>
       </c>
       <c r="K57" s="3">
         <v>1457300</v>
@@ -2573,25 +2573,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1221800</v>
+        <v>1240200</v>
       </c>
       <c r="E58" s="3">
-        <v>910100</v>
+        <v>923800</v>
       </c>
       <c r="F58" s="3">
-        <v>718500</v>
+        <v>729300</v>
       </c>
       <c r="G58" s="3">
-        <v>522700</v>
+        <v>530600</v>
       </c>
       <c r="H58" s="3">
-        <v>1772600</v>
+        <v>1799300</v>
       </c>
       <c r="I58" s="3">
-        <v>1482000</v>
+        <v>1504300</v>
       </c>
       <c r="J58" s="3">
-        <v>1526800</v>
+        <v>1549800</v>
       </c>
       <c r="K58" s="3">
         <v>1916500</v>
@@ -2615,25 +2615,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2835400</v>
+        <v>2878100</v>
       </c>
       <c r="E59" s="3">
-        <v>2516700</v>
+        <v>2554600</v>
       </c>
       <c r="F59" s="3">
-        <v>2311500</v>
+        <v>2346300</v>
       </c>
       <c r="G59" s="3">
-        <v>8570500</v>
+        <v>8699600</v>
       </c>
       <c r="H59" s="3">
-        <v>2450200</v>
+        <v>2487100</v>
       </c>
       <c r="I59" s="3">
-        <v>2462900</v>
+        <v>2500000</v>
       </c>
       <c r="J59" s="3">
-        <v>2534900</v>
+        <v>2573000</v>
       </c>
       <c r="K59" s="3">
         <v>2556600</v>
@@ -2657,25 +2657,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>5505300</v>
+        <v>5588200</v>
       </c>
       <c r="E60" s="3">
-        <v>4604500</v>
+        <v>4673800</v>
       </c>
       <c r="F60" s="3">
-        <v>4365900</v>
+        <v>4431700</v>
       </c>
       <c r="G60" s="3">
-        <v>10284700</v>
+        <v>10439600</v>
       </c>
       <c r="H60" s="3">
-        <v>5605500</v>
+        <v>5689900</v>
       </c>
       <c r="I60" s="3">
-        <v>5235800</v>
+        <v>5314600</v>
       </c>
       <c r="J60" s="3">
-        <v>5358000</v>
+        <v>5438700</v>
       </c>
       <c r="K60" s="3">
         <v>5930500</v>
@@ -2699,25 +2699,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1615200</v>
+        <v>1639600</v>
       </c>
       <c r="E61" s="3">
-        <v>1098800</v>
+        <v>1115400</v>
       </c>
       <c r="F61" s="3">
-        <v>1237800</v>
+        <v>1256400</v>
       </c>
       <c r="G61" s="3">
-        <v>1108300</v>
+        <v>1125000</v>
       </c>
       <c r="H61" s="3">
-        <v>4425300</v>
+        <v>4492000</v>
       </c>
       <c r="I61" s="3">
-        <v>4373800</v>
+        <v>4439700</v>
       </c>
       <c r="J61" s="3">
-        <v>4181900</v>
+        <v>4244800</v>
       </c>
       <c r="K61" s="3">
         <v>4351500</v>
@@ -2741,25 +2741,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>793500</v>
+        <v>805500</v>
       </c>
       <c r="E62" s="3">
-        <v>587600</v>
+        <v>596500</v>
       </c>
       <c r="F62" s="3">
-        <v>797400</v>
+        <v>809400</v>
       </c>
       <c r="G62" s="3">
-        <v>951600</v>
+        <v>965900</v>
       </c>
       <c r="H62" s="3">
-        <v>1298000</v>
+        <v>1317600</v>
       </c>
       <c r="I62" s="3">
-        <v>1361500</v>
+        <v>1382000</v>
       </c>
       <c r="J62" s="3">
-        <v>1365800</v>
+        <v>1386300</v>
       </c>
       <c r="K62" s="3">
         <v>1688900</v>
@@ -2909,25 +2909,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>8090200</v>
+        <v>8212000</v>
       </c>
       <c r="E66" s="3">
-        <v>6316000</v>
+        <v>6411200</v>
       </c>
       <c r="F66" s="3">
-        <v>6425000</v>
+        <v>6521800</v>
       </c>
       <c r="G66" s="3">
-        <v>12929900</v>
+        <v>13124600</v>
       </c>
       <c r="H66" s="3">
-        <v>11902600</v>
+        <v>12081800</v>
       </c>
       <c r="I66" s="3">
-        <v>11496900</v>
+        <v>11670100</v>
       </c>
       <c r="J66" s="3">
-        <v>11402100</v>
+        <v>11573800</v>
       </c>
       <c r="K66" s="3">
         <v>12485100</v>
@@ -3137,25 +3137,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>3125600</v>
+        <v>3172700</v>
       </c>
       <c r="E72" s="3">
-        <v>3053400</v>
+        <v>3099400</v>
       </c>
       <c r="F72" s="3">
-        <v>3728900</v>
+        <v>3785000</v>
       </c>
       <c r="G72" s="3">
-        <v>3949000</v>
+        <v>4008500</v>
       </c>
       <c r="H72" s="3">
-        <v>3817200</v>
+        <v>3874700</v>
       </c>
       <c r="I72" s="3">
-        <v>3387200</v>
+        <v>3438200</v>
       </c>
       <c r="J72" s="3">
-        <v>4365400</v>
+        <v>4431200</v>
       </c>
       <c r="K72" s="3">
         <v>4986400</v>
@@ -3305,25 +3305,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>6185500</v>
+        <v>6278700</v>
       </c>
       <c r="E76" s="3">
-        <v>5989600</v>
+        <v>6079800</v>
       </c>
       <c r="F76" s="3">
-        <v>6110400</v>
+        <v>6202500</v>
       </c>
       <c r="G76" s="3">
-        <v>6111300</v>
+        <v>6203300</v>
       </c>
       <c r="H76" s="3">
-        <v>6192300</v>
+        <v>6285600</v>
       </c>
       <c r="I76" s="3">
-        <v>6039500</v>
+        <v>6130500</v>
       </c>
       <c r="J76" s="3">
-        <v>6919600</v>
+        <v>7023800</v>
       </c>
       <c r="K76" s="3">
         <v>7921900</v>
@@ -3436,25 +3436,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>361000</v>
+        <v>366400</v>
       </c>
       <c r="E81" s="3">
-        <v>201700</v>
+        <v>204700</v>
       </c>
       <c r="F81" s="3">
-        <v>-217300</v>
+        <v>-220600</v>
       </c>
       <c r="G81" s="3">
-        <v>262600</v>
+        <v>266500</v>
       </c>
       <c r="H81" s="3">
-        <v>328900</v>
+        <v>333800</v>
       </c>
       <c r="I81" s="3">
-        <v>-898900</v>
+        <v>-912400</v>
       </c>
       <c r="J81" s="3">
-        <v>23200</v>
+        <v>23500</v>
       </c>
       <c r="K81" s="3">
         <v>462900</v>
@@ -3496,25 +3496,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>647200</v>
+        <v>656900</v>
       </c>
       <c r="E83" s="3">
-        <v>600800</v>
+        <v>609800</v>
       </c>
       <c r="F83" s="3">
-        <v>694700</v>
+        <v>705100</v>
       </c>
       <c r="G83" s="3">
-        <v>801400</v>
+        <v>813400</v>
       </c>
       <c r="H83" s="3">
-        <v>626100</v>
+        <v>635500</v>
       </c>
       <c r="I83" s="3">
-        <v>719300</v>
+        <v>730100</v>
       </c>
       <c r="J83" s="3">
-        <v>709700</v>
+        <v>720400</v>
       </c>
       <c r="K83" s="3">
         <v>789100</v>
@@ -3748,25 +3748,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>442900</v>
+        <v>449600</v>
       </c>
       <c r="E89" s="3">
-        <v>547500</v>
+        <v>555800</v>
       </c>
       <c r="F89" s="3">
-        <v>843000</v>
+        <v>855700</v>
       </c>
       <c r="G89" s="3">
-        <v>774900</v>
+        <v>786600</v>
       </c>
       <c r="H89" s="3">
-        <v>544100</v>
+        <v>552300</v>
       </c>
       <c r="I89" s="3">
-        <v>732300</v>
+        <v>743300</v>
       </c>
       <c r="J89" s="3">
-        <v>586300</v>
+        <v>595100</v>
       </c>
       <c r="K89" s="3">
         <v>734000</v>
@@ -3808,25 +3808,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-301800</v>
+        <v>-306400</v>
       </c>
       <c r="E91" s="3">
-        <v>-248100</v>
+        <v>-251800</v>
       </c>
       <c r="F91" s="3">
-        <v>-279900</v>
+        <v>-284100</v>
       </c>
       <c r="G91" s="3">
-        <v>-575000</v>
+        <v>-583700</v>
       </c>
       <c r="H91" s="3">
-        <v>-481100</v>
+        <v>-488400</v>
       </c>
       <c r="I91" s="3">
-        <v>-480000</v>
+        <v>-487200</v>
       </c>
       <c r="J91" s="3">
-        <v>-501000</v>
+        <v>-508500</v>
       </c>
       <c r="K91" s="3">
         <v>-615800</v>
@@ -3934,25 +3934,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-889400</v>
+        <v>-902700</v>
       </c>
       <c r="E94" s="3">
-        <v>-394100</v>
+        <v>-400100</v>
       </c>
       <c r="F94" s="3">
-        <v>-422000</v>
+        <v>-428400</v>
       </c>
       <c r="G94" s="3">
-        <v>-1092900</v>
+        <v>-1109300</v>
       </c>
       <c r="H94" s="3">
-        <v>-305000</v>
+        <v>-309600</v>
       </c>
       <c r="I94" s="3">
-        <v>-538400</v>
+        <v>-546500</v>
       </c>
       <c r="J94" s="3">
-        <v>-708600</v>
+        <v>-719300</v>
       </c>
       <c r="K94" s="3">
         <v>-765400</v>
@@ -3994,25 +3994,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-123700</v>
+        <v>-125600</v>
       </c>
       <c r="E96" s="3">
-        <v>-93300</v>
+        <v>-94800</v>
       </c>
       <c r="F96" s="3">
-        <v>-98600</v>
+        <v>-100100</v>
       </c>
       <c r="G96" s="3">
-        <v>-125100</v>
+        <v>-127000</v>
       </c>
       <c r="H96" s="3">
-        <v>-84200</v>
+        <v>-85500</v>
       </c>
       <c r="I96" s="3">
-        <v>-96300</v>
+        <v>-97700</v>
       </c>
       <c r="J96" s="3">
-        <v>-192500</v>
+        <v>-195400</v>
       </c>
       <c r="K96" s="3">
         <v>-183800</v>
@@ -4162,25 +4162,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>235400</v>
+        <v>239000</v>
       </c>
       <c r="E100" s="3">
-        <v>-874400</v>
+        <v>-887600</v>
       </c>
       <c r="F100" s="3">
-        <v>-27100</v>
+        <v>-27500</v>
       </c>
       <c r="G100" s="3">
-        <v>503000</v>
+        <v>510600</v>
       </c>
       <c r="H100" s="3">
-        <v>281700</v>
+        <v>285900</v>
       </c>
       <c r="I100" s="3">
-        <v>42500</v>
+        <v>43200</v>
       </c>
       <c r="J100" s="3">
-        <v>-132300</v>
+        <v>-134300</v>
       </c>
       <c r="K100" s="3">
         <v>313600</v>
@@ -4204,25 +4204,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>57400</v>
+        <v>58200</v>
       </c>
       <c r="E101" s="3">
-        <v>81400</v>
+        <v>82600</v>
       </c>
       <c r="F101" s="3">
-        <v>48700</v>
+        <v>49500</v>
       </c>
       <c r="G101" s="3">
-        <v>-28400</v>
+        <v>-28800</v>
       </c>
       <c r="H101" s="3">
-        <v>7200</v>
+        <v>7400</v>
       </c>
       <c r="I101" s="3">
-        <v>-9800</v>
+        <v>-10000</v>
       </c>
       <c r="J101" s="3">
-        <v>-18500</v>
+        <v>-18700</v>
       </c>
       <c r="K101" s="3">
         <v>-62900</v>
@@ -4246,25 +4246,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-153600</v>
+        <v>-155900</v>
       </c>
       <c r="E102" s="3">
-        <v>-639600</v>
+        <v>-649200</v>
       </c>
       <c r="F102" s="3">
-        <v>442600</v>
+        <v>449300</v>
       </c>
       <c r="G102" s="3">
-        <v>156600</v>
+        <v>159000</v>
       </c>
       <c r="H102" s="3">
-        <v>528100</v>
+        <v>536000</v>
       </c>
       <c r="I102" s="3">
-        <v>226700</v>
+        <v>230100</v>
       </c>
       <c r="J102" s="3">
-        <v>-273000</v>
+        <v>-277100</v>
       </c>
       <c r="K102" s="3">
         <v>219200</v>

--- a/AAII_Financials/Yearly/RICOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RICOY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
   <si>
     <t>RICOY</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45016</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44651</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44286</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43921</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43555</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43190</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42825</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42460</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42094</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41729</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41364</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40999</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>14384400</v>
+        <v>14986500</v>
       </c>
       <c r="E8" s="3">
-        <v>11852900</v>
+        <v>13616100</v>
       </c>
       <c r="F8" s="3">
-        <v>11337100</v>
+        <v>11219800</v>
       </c>
       <c r="G8" s="3">
-        <v>13537800</v>
+        <v>10731600</v>
       </c>
       <c r="H8" s="3">
-        <v>13569200</v>
+        <v>12814700</v>
       </c>
       <c r="I8" s="3">
-        <v>13907100</v>
+        <v>12844400</v>
       </c>
       <c r="J8" s="3">
+        <v>13164300</v>
+      </c>
+      <c r="K8" s="3">
         <v>13674800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>16236400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>18351500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20112600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>17143700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>17207400</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>9360200</v>
+        <v>9754300</v>
       </c>
       <c r="E9" s="3">
-        <v>7656100</v>
+        <v>8860300</v>
       </c>
       <c r="F9" s="3">
-        <v>7479800</v>
+        <v>7247200</v>
       </c>
       <c r="G9" s="3">
-        <v>8672800</v>
+        <v>7080300</v>
       </c>
       <c r="H9" s="3">
-        <v>8400400</v>
+        <v>8209600</v>
       </c>
       <c r="I9" s="3">
-        <v>8575700</v>
+        <v>7951700</v>
       </c>
       <c r="J9" s="3">
+        <v>8117600</v>
+      </c>
+      <c r="K9" s="3">
         <v>8359400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9753900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10615500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>12113800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>20836800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10403700</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>5024100</v>
+        <v>5232200</v>
       </c>
       <c r="E10" s="3">
-        <v>4196800</v>
+        <v>4755800</v>
       </c>
       <c r="F10" s="3">
-        <v>3857300</v>
+        <v>3972600</v>
       </c>
       <c r="G10" s="3">
-        <v>4865000</v>
+        <v>3651300</v>
       </c>
       <c r="H10" s="3">
-        <v>5168800</v>
+        <v>4605200</v>
       </c>
       <c r="I10" s="3">
-        <v>5331400</v>
+        <v>4892700</v>
       </c>
       <c r="J10" s="3">
+        <v>5046600</v>
+      </c>
+      <c r="K10" s="3">
         <v>5315400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6482400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>7736000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>7998700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-3693100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>6803700</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,50 +873,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
-        <v>575000</v>
+      <c r="D12" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E12" s="3">
-        <v>510400</v>
+        <v>544300</v>
       </c>
       <c r="F12" s="3">
-        <v>533800</v>
+        <v>483100</v>
       </c>
       <c r="G12" s="3">
-        <v>594600</v>
+        <v>505300</v>
       </c>
       <c r="H12" s="3">
-        <v>633700</v>
+        <v>562900</v>
       </c>
       <c r="I12" s="3">
-        <v>633500</v>
+        <v>599900</v>
       </c>
       <c r="J12" s="3">
+        <v>599600</v>
+      </c>
+      <c r="K12" s="3">
         <v>676600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>750000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>838400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>864400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1831000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1076000</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -944,93 +960,102 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-4800</v>
+        <v>3900</v>
       </c>
       <c r="E14" s="3">
-        <v>13600</v>
+        <v>-4500</v>
       </c>
       <c r="F14" s="3">
-        <v>335500</v>
+        <v>12900</v>
       </c>
       <c r="G14" s="3">
-        <v>75900</v>
+        <v>317600</v>
       </c>
       <c r="H14" s="3">
-        <v>144400</v>
+        <v>71800</v>
       </c>
       <c r="I14" s="3">
-        <v>1359600</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>10</v>
+        <v>136700</v>
+      </c>
+      <c r="J14" s="3">
+        <v>1286900</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M14" s="3">
         <v>8600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>103700</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>293800</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>382400</v>
+      <c r="D15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E15" s="3">
-        <v>339300</v>
+        <v>362000</v>
       </c>
       <c r="F15" s="3">
-        <v>366800</v>
+        <v>321100</v>
       </c>
       <c r="G15" s="3">
-        <v>359500</v>
+        <v>347200</v>
       </c>
       <c r="H15" s="3">
-        <v>167600</v>
+        <v>340300</v>
       </c>
       <c r="I15" s="3">
-        <v>270200</v>
+        <v>158600</v>
       </c>
       <c r="J15" s="3">
+        <v>255800</v>
+      </c>
+      <c r="K15" s="3">
         <v>271500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>273000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>318200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>339900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>321800</v>
       </c>
-      <c r="O15" s="3" t="s">
+      <c r="P15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>13853700</v>
+        <v>14590800</v>
       </c>
       <c r="E17" s="3">
-        <v>11582900</v>
+        <v>13113700</v>
       </c>
       <c r="F17" s="3">
-        <v>11643300</v>
+        <v>10964300</v>
       </c>
       <c r="G17" s="3">
-        <v>13005100</v>
+        <v>11021400</v>
       </c>
       <c r="H17" s="3">
-        <v>12983900</v>
+        <v>12310500</v>
       </c>
       <c r="I17" s="3">
-        <v>14686700</v>
+        <v>12290400</v>
       </c>
       <c r="J17" s="3">
+        <v>13902300</v>
+      </c>
+      <c r="K17" s="3">
         <v>13446400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15484500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>17364000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>19010200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>16475100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>17416100</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>530700</v>
+        <v>395700</v>
       </c>
       <c r="E18" s="3">
-        <v>270000</v>
+        <v>502400</v>
       </c>
       <c r="F18" s="3">
-        <v>-306200</v>
+        <v>255500</v>
       </c>
       <c r="G18" s="3">
-        <v>532700</v>
+        <v>-289800</v>
       </c>
       <c r="H18" s="3">
-        <v>585300</v>
+        <v>504300</v>
       </c>
       <c r="I18" s="3">
-        <v>-779700</v>
+        <v>554000</v>
       </c>
       <c r="J18" s="3">
+        <v>-738000</v>
+      </c>
+      <c r="K18" s="3">
         <v>228400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>751900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>987500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1102400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>668600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-208600</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,218 +1178,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>57800</v>
+        <v>39400</v>
       </c>
       <c r="E20" s="3">
-        <v>51200</v>
+        <v>54800</v>
       </c>
       <c r="F20" s="3">
-        <v>50200</v>
+        <v>48500</v>
       </c>
       <c r="G20" s="3">
-        <v>17700</v>
+        <v>47500</v>
       </c>
       <c r="H20" s="3">
-        <v>20800</v>
+        <v>16700</v>
       </c>
       <c r="I20" s="3">
-        <v>-12000</v>
+        <v>19700</v>
       </c>
       <c r="J20" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="K20" s="3">
         <v>24400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>31100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>47400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>84400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-17000</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1248400</v>
+        <v>1129600</v>
       </c>
       <c r="E21" s="3">
-        <v>933700</v>
+        <v>1178000</v>
       </c>
       <c r="F21" s="3">
-        <v>452200</v>
+        <v>880300</v>
       </c>
       <c r="G21" s="3">
-        <v>1367500</v>
+        <v>424100</v>
       </c>
       <c r="H21" s="3">
-        <v>1244400</v>
+        <v>1289800</v>
       </c>
       <c r="I21" s="3">
-        <v>-58300</v>
+        <v>1174400</v>
       </c>
       <c r="J21" s="3">
+        <v>-59300</v>
+      </c>
+      <c r="K21" s="3">
         <v>976400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1533000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1949200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2127000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1626800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>599200</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>40500</v>
+      <c r="D22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E22" s="3">
-        <v>22000</v>
+        <v>38400</v>
       </c>
       <c r="F22" s="3">
-        <v>20500</v>
+        <v>20800</v>
       </c>
       <c r="G22" s="3">
-        <v>38900</v>
+        <v>19400</v>
       </c>
       <c r="H22" s="3">
-        <v>40200</v>
+        <v>36800</v>
       </c>
       <c r="I22" s="3">
-        <v>45300</v>
+        <v>38100</v>
       </c>
       <c r="J22" s="3">
+        <v>42900</v>
+      </c>
+      <c r="K22" s="3">
         <v>50900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>48100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>60700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>68300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>134100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>63100</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>548000</v>
+        <v>435100</v>
       </c>
       <c r="E23" s="3">
-        <v>299200</v>
+        <v>518700</v>
       </c>
       <c r="F23" s="3">
-        <v>-276500</v>
+        <v>283200</v>
       </c>
       <c r="G23" s="3">
-        <v>511500</v>
+        <v>-261800</v>
       </c>
       <c r="H23" s="3">
-        <v>565900</v>
+        <v>484200</v>
       </c>
       <c r="I23" s="3">
-        <v>-837000</v>
+        <v>535700</v>
       </c>
       <c r="J23" s="3">
+        <v>-792300</v>
+      </c>
+      <c r="K23" s="3">
         <v>201900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>703300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>957900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1081500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>618900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-288700</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>173000</v>
+        <v>152900</v>
       </c>
       <c r="E24" s="3">
-        <v>92800</v>
+        <v>163800</v>
       </c>
       <c r="F24" s="3">
-        <v>-56400</v>
+        <v>87800</v>
       </c>
       <c r="G24" s="3">
-        <v>212200</v>
+        <v>-53400</v>
       </c>
       <c r="H24" s="3">
-        <v>192700</v>
+        <v>200800</v>
       </c>
       <c r="I24" s="3">
-        <v>27900</v>
+        <v>182400</v>
       </c>
       <c r="J24" s="3">
+        <v>26400</v>
+      </c>
+      <c r="K24" s="3">
         <v>138300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>208600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>329200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>362800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>220600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>74300</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>375000</v>
+        <v>282300</v>
       </c>
       <c r="E26" s="3">
-        <v>206400</v>
+        <v>355000</v>
       </c>
       <c r="F26" s="3">
-        <v>-220200</v>
+        <v>195400</v>
       </c>
       <c r="G26" s="3">
-        <v>299300</v>
+        <v>-208400</v>
       </c>
       <c r="H26" s="3">
-        <v>373200</v>
+        <v>283400</v>
       </c>
       <c r="I26" s="3">
-        <v>-864900</v>
+        <v>353300</v>
       </c>
       <c r="J26" s="3">
+        <v>-818700</v>
+      </c>
+      <c r="K26" s="3">
         <v>63600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>494700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>628700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>718600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>398300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-363000</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>366400</v>
+        <v>281800</v>
       </c>
       <c r="E27" s="3">
-        <v>204700</v>
+        <v>346900</v>
       </c>
       <c r="F27" s="3">
-        <v>-220600</v>
+        <v>193800</v>
       </c>
       <c r="G27" s="3">
-        <v>266500</v>
+        <v>-208800</v>
       </c>
       <c r="H27" s="3">
-        <v>333800</v>
+        <v>252300</v>
       </c>
       <c r="I27" s="3">
-        <v>-903600</v>
+        <v>316000</v>
       </c>
       <c r="J27" s="3">
+        <v>-855300</v>
+      </c>
+      <c r="K27" s="3">
         <v>23500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>462900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>584800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>667000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>309500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-402800</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1544,11 +1604,11 @@
       <c r="H29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I29" s="3">
-        <v>-8800</v>
-      </c>
-      <c r="J29" s="3" t="s">
+      <c r="I29" s="3" t="s">
         <v>10</v>
+      </c>
+      <c r="J29" s="3">
+        <v>-8400</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>10</v>
@@ -1565,9 +1625,12 @@
       <c r="O29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-57800</v>
+        <v>-39400</v>
       </c>
       <c r="E32" s="3">
-        <v>-51200</v>
+        <v>-54800</v>
       </c>
       <c r="F32" s="3">
-        <v>-50200</v>
+        <v>-48500</v>
       </c>
       <c r="G32" s="3">
-        <v>-17700</v>
+        <v>-47500</v>
       </c>
       <c r="H32" s="3">
-        <v>-20800</v>
+        <v>-16700</v>
       </c>
       <c r="I32" s="3">
-        <v>12000</v>
+        <v>-19700</v>
       </c>
       <c r="J32" s="3">
+        <v>11400</v>
+      </c>
+      <c r="K32" s="3">
         <v>-24400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-31100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-47400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-84400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>17000</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>366400</v>
+        <v>281800</v>
       </c>
       <c r="E33" s="3">
-        <v>204700</v>
+        <v>346900</v>
       </c>
       <c r="F33" s="3">
-        <v>-220600</v>
+        <v>193800</v>
       </c>
       <c r="G33" s="3">
-        <v>266500</v>
+        <v>-208800</v>
       </c>
       <c r="H33" s="3">
-        <v>333800</v>
+        <v>252300</v>
       </c>
       <c r="I33" s="3">
-        <v>-912400</v>
+        <v>316000</v>
       </c>
       <c r="J33" s="3">
+        <v>-863700</v>
+      </c>
+      <c r="K33" s="3">
         <v>23500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>462900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>584800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>667000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>309500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-402800</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>366400</v>
+        <v>281800</v>
       </c>
       <c r="E35" s="3">
-        <v>204700</v>
+        <v>346900</v>
       </c>
       <c r="F35" s="3">
-        <v>-220600</v>
+        <v>193800</v>
       </c>
       <c r="G35" s="3">
-        <v>266500</v>
+        <v>-208800</v>
       </c>
       <c r="H35" s="3">
-        <v>333800</v>
+        <v>252300</v>
       </c>
       <c r="I35" s="3">
-        <v>-912400</v>
+        <v>316000</v>
       </c>
       <c r="J35" s="3">
+        <v>-863700</v>
+      </c>
+      <c r="K35" s="3">
         <v>23500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>462900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>584800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>667000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>309500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-402800</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45016</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44651</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44286</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43921</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43555</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43190</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42825</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42460</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42094</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41729</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41364</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40999</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,386 +1986,414 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1495500</v>
+        <v>1129600</v>
       </c>
       <c r="E41" s="3">
-        <v>1619700</v>
+        <v>1415700</v>
       </c>
       <c r="F41" s="3">
-        <v>2256600</v>
+        <v>1533200</v>
       </c>
       <c r="G41" s="3">
-        <v>1771500</v>
+        <v>2136100</v>
       </c>
       <c r="H41" s="3">
-        <v>1618300</v>
+        <v>1676900</v>
       </c>
       <c r="I41" s="3">
-        <v>1082200</v>
+        <v>1531800</v>
       </c>
       <c r="J41" s="3">
+        <v>1024400</v>
+      </c>
+      <c r="K41" s="3">
         <v>852100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1238600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1182700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1320000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2187600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1412100</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>634300</v>
+        <v>684100</v>
       </c>
       <c r="E42" s="3">
-        <v>622600</v>
+        <v>600400</v>
       </c>
       <c r="F42" s="3">
-        <v>627200</v>
+        <v>589300</v>
       </c>
       <c r="G42" s="3">
-        <v>588200</v>
+        <v>593700</v>
       </c>
       <c r="H42" s="3">
-        <v>1984400</v>
+        <v>556800</v>
       </c>
       <c r="I42" s="3">
-        <v>2339700</v>
+        <v>1878400</v>
       </c>
       <c r="J42" s="3">
+        <v>2214700</v>
+      </c>
+      <c r="K42" s="3">
         <v>1922500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2001800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2218300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2287100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2103200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>22200</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3211100</v>
+        <v>3432800</v>
       </c>
       <c r="E43" s="3">
-        <v>2676800</v>
+        <v>3039600</v>
       </c>
       <c r="F43" s="3">
-        <v>2643000</v>
+        <v>2533800</v>
       </c>
       <c r="G43" s="3">
-        <v>2647300</v>
+        <v>2501800</v>
       </c>
       <c r="H43" s="3">
-        <v>4076400</v>
+        <v>2505900</v>
       </c>
       <c r="I43" s="3">
-        <v>3974900</v>
+        <v>3858600</v>
       </c>
       <c r="J43" s="3">
+        <v>3762500</v>
+      </c>
+      <c r="K43" s="3">
         <v>3817000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4146900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4721600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9979400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>8964400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6209800</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>2118800</v>
+        <v>1917800</v>
       </c>
       <c r="E44" s="3">
-        <v>1567400</v>
+        <v>2005700</v>
       </c>
       <c r="F44" s="3">
-        <v>1294200</v>
+        <v>1483700</v>
       </c>
       <c r="G44" s="3">
-        <v>1356400</v>
+        <v>1225100</v>
       </c>
       <c r="H44" s="3">
-        <v>1400200</v>
+        <v>1284000</v>
       </c>
       <c r="I44" s="3">
-        <v>1216500</v>
+        <v>1325400</v>
       </c>
       <c r="J44" s="3">
+        <v>1151500</v>
+      </c>
+      <c r="K44" s="3">
         <v>1365200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1522100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1914800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1778600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3563900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1762900</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>461700</v>
+        <v>512800</v>
       </c>
       <c r="E45" s="3">
-        <v>337200</v>
+        <v>437000</v>
       </c>
       <c r="F45" s="3">
-        <v>314900</v>
+        <v>319200</v>
       </c>
       <c r="G45" s="3">
-        <v>7831900</v>
+        <v>298100</v>
       </c>
       <c r="H45" s="3">
-        <v>287700</v>
+        <v>7413600</v>
       </c>
       <c r="I45" s="3">
-        <v>337400</v>
+        <v>272400</v>
       </c>
       <c r="J45" s="3">
+        <v>319300</v>
+      </c>
+      <c r="K45" s="3">
         <v>395500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>448600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>338300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>314300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3011200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>595700</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>7921500</v>
+        <v>7677100</v>
       </c>
       <c r="E46" s="3">
-        <v>6823700</v>
+        <v>7498400</v>
       </c>
       <c r="F46" s="3">
-        <v>7135900</v>
+        <v>6459300</v>
       </c>
       <c r="G46" s="3">
-        <v>14195400</v>
+        <v>6754800</v>
       </c>
       <c r="H46" s="3">
-        <v>9367000</v>
+        <v>13437200</v>
       </c>
       <c r="I46" s="3">
-        <v>8950600</v>
+        <v>8866700</v>
       </c>
       <c r="J46" s="3">
+        <v>8472500</v>
+      </c>
+      <c r="K46" s="3">
         <v>8352300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9358000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10375700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>10689700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9593000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10002800</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1604400</v>
+        <v>1752600</v>
       </c>
       <c r="E47" s="3">
-        <v>1496600</v>
+        <v>1518700</v>
       </c>
       <c r="F47" s="3">
-        <v>1577800</v>
+        <v>1416700</v>
       </c>
       <c r="G47" s="3">
-        <v>1135300</v>
+        <v>1493600</v>
       </c>
       <c r="H47" s="3">
-        <v>5009600</v>
+        <v>1074600</v>
       </c>
       <c r="I47" s="3">
-        <v>4854900</v>
+        <v>4742000</v>
       </c>
       <c r="J47" s="3">
+        <v>4595600</v>
+      </c>
+      <c r="K47" s="3">
         <v>4972400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5058200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5633900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5612200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>5473000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4645800</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1708700</v>
+        <v>1698800</v>
       </c>
       <c r="E48" s="3">
-        <v>1659200</v>
+        <v>1617400</v>
       </c>
       <c r="F48" s="3">
-        <v>1722900</v>
+        <v>1570600</v>
       </c>
       <c r="G48" s="3">
-        <v>1759100</v>
+        <v>1630800</v>
       </c>
       <c r="H48" s="3">
-        <v>1686900</v>
+        <v>1665100</v>
       </c>
       <c r="I48" s="3">
-        <v>1685000</v>
+        <v>1596800</v>
       </c>
       <c r="J48" s="3">
+        <v>1595000</v>
+      </c>
+      <c r="K48" s="3">
         <v>1828300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2032600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2359500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2894700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5065200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2427500</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2469500</v>
+        <v>2631500</v>
       </c>
       <c r="E49" s="3">
-        <v>1748900</v>
+        <v>2337600</v>
       </c>
       <c r="F49" s="3">
-        <v>1519900</v>
+        <v>1655500</v>
       </c>
       <c r="G49" s="3">
-        <v>1563000</v>
+        <v>1438800</v>
       </c>
       <c r="H49" s="3">
-        <v>1481500</v>
+        <v>1479500</v>
       </c>
       <c r="I49" s="3">
-        <v>1463500</v>
+        <v>1402400</v>
       </c>
       <c r="J49" s="3">
+        <v>1385300</v>
+      </c>
+      <c r="K49" s="3">
         <v>2616300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3041700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3717000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3658100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4520200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2785800</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>786600</v>
+        <v>825800</v>
       </c>
       <c r="E52" s="3">
-        <v>762500</v>
+        <v>744600</v>
       </c>
       <c r="F52" s="3">
-        <v>767700</v>
+        <v>721800</v>
       </c>
       <c r="G52" s="3">
-        <v>675100</v>
+        <v>726700</v>
       </c>
       <c r="H52" s="3">
-        <v>822400</v>
+        <v>639100</v>
       </c>
       <c r="I52" s="3">
-        <v>846500</v>
+        <v>778500</v>
       </c>
       <c r="J52" s="3">
+        <v>801300</v>
+      </c>
+      <c r="K52" s="3">
         <v>828300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>916500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1202500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1345400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6546100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>833900</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>14490700</v>
+        <v>14585800</v>
       </c>
       <c r="E54" s="3">
-        <v>12490900</v>
+        <v>13716700</v>
       </c>
       <c r="F54" s="3">
-        <v>12724200</v>
+        <v>11823800</v>
       </c>
       <c r="G54" s="3">
-        <v>19327900</v>
+        <v>12044600</v>
       </c>
       <c r="H54" s="3">
-        <v>18367400</v>
+        <v>18295600</v>
       </c>
       <c r="I54" s="3">
-        <v>17800500</v>
+        <v>17386300</v>
       </c>
       <c r="J54" s="3">
+        <v>16849800</v>
+      </c>
+      <c r="K54" s="3">
         <v>18597600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>20407000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>23288700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>23785000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>21735700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>20695800</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,260 +2654,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1469900</v>
+        <v>1947700</v>
       </c>
       <c r="E57" s="3">
-        <v>1195500</v>
+        <v>1391400</v>
       </c>
       <c r="F57" s="3">
-        <v>1356100</v>
+        <v>1131600</v>
       </c>
       <c r="G57" s="3">
-        <v>1209400</v>
+        <v>1283600</v>
       </c>
       <c r="H57" s="3">
-        <v>1403500</v>
+        <v>1144800</v>
       </c>
       <c r="I57" s="3">
-        <v>1310300</v>
+        <v>1328500</v>
       </c>
       <c r="J57" s="3">
+        <v>1240400</v>
+      </c>
+      <c r="K57" s="3">
         <v>1315800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1457300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2362700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1965300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3862300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2175500</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1240200</v>
+        <v>1117400</v>
       </c>
       <c r="E58" s="3">
-        <v>923800</v>
+        <v>1174000</v>
       </c>
       <c r="F58" s="3">
-        <v>729300</v>
+        <v>874400</v>
       </c>
       <c r="G58" s="3">
-        <v>530600</v>
+        <v>690400</v>
       </c>
       <c r="H58" s="3">
-        <v>1799300</v>
+        <v>502200</v>
       </c>
       <c r="I58" s="3">
-        <v>1504300</v>
+        <v>1703200</v>
       </c>
       <c r="J58" s="3">
+        <v>1424000</v>
+      </c>
+      <c r="K58" s="3">
         <v>1549800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1916500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1894200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2489400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4128200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2061000</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2878100</v>
+        <v>2544700</v>
       </c>
       <c r="E59" s="3">
-        <v>2554600</v>
+        <v>2724400</v>
       </c>
       <c r="F59" s="3">
-        <v>2346300</v>
+        <v>2418100</v>
       </c>
       <c r="G59" s="3">
-        <v>8699600</v>
+        <v>2221000</v>
       </c>
       <c r="H59" s="3">
-        <v>2487100</v>
+        <v>8234900</v>
       </c>
       <c r="I59" s="3">
-        <v>2500000</v>
+        <v>2354300</v>
       </c>
       <c r="J59" s="3">
+        <v>2366400</v>
+      </c>
+      <c r="K59" s="3">
         <v>2573000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2556600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2329400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3200300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4746300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1847600</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>5588200</v>
+        <v>5609800</v>
       </c>
       <c r="E60" s="3">
-        <v>4673800</v>
+        <v>5289700</v>
       </c>
       <c r="F60" s="3">
-        <v>4431700</v>
+        <v>4424200</v>
       </c>
       <c r="G60" s="3">
-        <v>10439600</v>
+        <v>4195000</v>
       </c>
       <c r="H60" s="3">
-        <v>5689900</v>
+        <v>9882000</v>
       </c>
       <c r="I60" s="3">
-        <v>5314600</v>
+        <v>5386000</v>
       </c>
       <c r="J60" s="3">
+        <v>5030800</v>
+      </c>
+      <c r="K60" s="3">
         <v>5438700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5930500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6586300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7654900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6370500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6084100</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1639600</v>
+        <v>1562700</v>
       </c>
       <c r="E61" s="3">
-        <v>1115400</v>
+        <v>1552000</v>
       </c>
       <c r="F61" s="3">
-        <v>1256400</v>
+        <v>1055800</v>
       </c>
       <c r="G61" s="3">
-        <v>1125000</v>
+        <v>1189300</v>
       </c>
       <c r="H61" s="3">
-        <v>4492000</v>
+        <v>1064900</v>
       </c>
       <c r="I61" s="3">
-        <v>4439700</v>
+        <v>4252000</v>
       </c>
       <c r="J61" s="3">
+        <v>4202600</v>
+      </c>
+      <c r="K61" s="3">
         <v>4244800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4351500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4849400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4143900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4314000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4749900</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>805500</v>
+        <v>617800</v>
       </c>
       <c r="E62" s="3">
-        <v>596500</v>
+        <v>762400</v>
       </c>
       <c r="F62" s="3">
-        <v>809400</v>
+        <v>564600</v>
       </c>
       <c r="G62" s="3">
-        <v>965900</v>
+        <v>766200</v>
       </c>
       <c r="H62" s="3">
-        <v>1317600</v>
+        <v>914300</v>
       </c>
       <c r="I62" s="3">
-        <v>1382000</v>
+        <v>1247200</v>
       </c>
       <c r="J62" s="3">
+        <v>1308200</v>
+      </c>
+      <c r="K62" s="3">
         <v>1386300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1688900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2006600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1961500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4245400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1915400</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>8212000</v>
+        <v>7958800</v>
       </c>
       <c r="E66" s="3">
-        <v>6411200</v>
+        <v>7773400</v>
       </c>
       <c r="F66" s="3">
-        <v>6521800</v>
+        <v>6068700</v>
       </c>
       <c r="G66" s="3">
-        <v>13124600</v>
+        <v>6173400</v>
       </c>
       <c r="H66" s="3">
-        <v>12081800</v>
+        <v>12423600</v>
       </c>
       <c r="I66" s="3">
-        <v>11670100</v>
+        <v>11436500</v>
       </c>
       <c r="J66" s="3">
+        <v>11046700</v>
+      </c>
+      <c r="K66" s="3">
         <v>11573800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>12485100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14040700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14355600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13430100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13258600</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>3172700</v>
+        <v>3197300</v>
       </c>
       <c r="E72" s="3">
-        <v>3099400</v>
+        <v>3003200</v>
       </c>
       <c r="F72" s="3">
-        <v>3785000</v>
+        <v>2933900</v>
       </c>
       <c r="G72" s="3">
-        <v>4008500</v>
+        <v>3582900</v>
       </c>
       <c r="H72" s="3">
-        <v>3874700</v>
+        <v>3794400</v>
       </c>
       <c r="I72" s="3">
-        <v>3438200</v>
+        <v>3667700</v>
       </c>
       <c r="J72" s="3">
+        <v>3254500</v>
+      </c>
+      <c r="K72" s="3">
         <v>4431200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4986400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5514400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5728100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>12094900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6712600</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>6278700</v>
+        <v>6627000</v>
       </c>
       <c r="E76" s="3">
-        <v>6079800</v>
+        <v>5943300</v>
       </c>
       <c r="F76" s="3">
-        <v>6202500</v>
+        <v>5755000</v>
       </c>
       <c r="G76" s="3">
-        <v>6203300</v>
+        <v>5871200</v>
       </c>
       <c r="H76" s="3">
-        <v>6285600</v>
+        <v>5872000</v>
       </c>
       <c r="I76" s="3">
-        <v>6130500</v>
+        <v>5949800</v>
       </c>
       <c r="J76" s="3">
+        <v>5803000</v>
+      </c>
+      <c r="K76" s="3">
         <v>7023800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7921900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9247900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9429400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8305600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7437200</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45016</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44651</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44286</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43921</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43555</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43190</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42825</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42460</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42094</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41729</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41364</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40999</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>366400</v>
+        <v>281800</v>
       </c>
       <c r="E81" s="3">
-        <v>204700</v>
+        <v>346900</v>
       </c>
       <c r="F81" s="3">
-        <v>-220600</v>
+        <v>193800</v>
       </c>
       <c r="G81" s="3">
-        <v>266500</v>
+        <v>-208800</v>
       </c>
       <c r="H81" s="3">
-        <v>333800</v>
+        <v>252300</v>
       </c>
       <c r="I81" s="3">
-        <v>-912400</v>
+        <v>316000</v>
       </c>
       <c r="J81" s="3">
+        <v>-863700</v>
+      </c>
+      <c r="K81" s="3">
         <v>23500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>462900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>584800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>667000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>309500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-402800</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>656900</v>
+        <v>695600</v>
       </c>
       <c r="E83" s="3">
-        <v>609800</v>
+        <v>621800</v>
       </c>
       <c r="F83" s="3">
-        <v>705100</v>
+        <v>577300</v>
       </c>
       <c r="G83" s="3">
-        <v>813400</v>
+        <v>667500</v>
       </c>
       <c r="H83" s="3">
-        <v>635500</v>
+        <v>770000</v>
       </c>
       <c r="I83" s="3">
-        <v>730100</v>
+        <v>601600</v>
       </c>
       <c r="J83" s="3">
+        <v>691100</v>
+      </c>
+      <c r="K83" s="3">
         <v>720400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>789100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>919800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>973100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>871900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>823900</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>449600</v>
+        <v>801400</v>
       </c>
       <c r="E89" s="3">
-        <v>555800</v>
+        <v>425600</v>
       </c>
       <c r="F89" s="3">
-        <v>855700</v>
+        <v>526100</v>
       </c>
       <c r="G89" s="3">
-        <v>786600</v>
+        <v>810000</v>
       </c>
       <c r="H89" s="3">
-        <v>552300</v>
+        <v>744600</v>
       </c>
       <c r="I89" s="3">
-        <v>743300</v>
+        <v>522800</v>
       </c>
       <c r="J89" s="3">
+        <v>703600</v>
+      </c>
+      <c r="K89" s="3">
         <v>595100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>734000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>874700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1345500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1248200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>101300</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-306400</v>
+        <v>-339800</v>
       </c>
       <c r="E91" s="3">
-        <v>-251800</v>
+        <v>-290000</v>
       </c>
       <c r="F91" s="3">
-        <v>-284100</v>
+        <v>-238400</v>
       </c>
       <c r="G91" s="3">
-        <v>-583700</v>
+        <v>-268900</v>
       </c>
       <c r="H91" s="3">
-        <v>-488400</v>
+        <v>-552500</v>
       </c>
       <c r="I91" s="3">
-        <v>-487200</v>
+        <v>-462300</v>
       </c>
       <c r="J91" s="3">
+        <v>-461200</v>
+      </c>
+      <c r="K91" s="3">
         <v>-508500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-615800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-648100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-668600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1507600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-662400</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-902700</v>
+        <v>-624100</v>
       </c>
       <c r="E94" s="3">
-        <v>-400100</v>
+        <v>-854500</v>
       </c>
       <c r="F94" s="3">
-        <v>-428400</v>
+        <v>-378700</v>
       </c>
       <c r="G94" s="3">
-        <v>-1109300</v>
+        <v>-405500</v>
       </c>
       <c r="H94" s="3">
-        <v>-309600</v>
+        <v>-1050100</v>
       </c>
       <c r="I94" s="3">
-        <v>-546500</v>
+        <v>-293000</v>
       </c>
       <c r="J94" s="3">
+        <v>-517300</v>
+      </c>
+      <c r="K94" s="3">
         <v>-719300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-765400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1223700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1126100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1106600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1016500</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,50 +4220,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-125600</v>
+        <v>-136000</v>
       </c>
       <c r="E96" s="3">
-        <v>-94800</v>
+        <v>-118900</v>
       </c>
       <c r="F96" s="3">
-        <v>-100100</v>
+        <v>-89700</v>
       </c>
       <c r="G96" s="3">
-        <v>-127000</v>
+        <v>-94700</v>
       </c>
       <c r="H96" s="3">
-        <v>-85500</v>
+        <v>-120200</v>
       </c>
       <c r="I96" s="3">
-        <v>-97700</v>
+        <v>-80900</v>
       </c>
       <c r="J96" s="3">
+        <v>-92500</v>
+      </c>
+      <c r="K96" s="3">
         <v>-195400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-183800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-207200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-219200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-138400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-216400</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>239000</v>
+        <v>-529000</v>
       </c>
       <c r="E100" s="3">
-        <v>-887600</v>
+        <v>226200</v>
       </c>
       <c r="F100" s="3">
-        <v>-27500</v>
+        <v>-840200</v>
       </c>
       <c r="G100" s="3">
-        <v>510600</v>
+        <v>-26100</v>
       </c>
       <c r="H100" s="3">
-        <v>285900</v>
+        <v>483300</v>
       </c>
       <c r="I100" s="3">
-        <v>43200</v>
+        <v>270700</v>
       </c>
       <c r="J100" s="3">
+        <v>40900</v>
+      </c>
+      <c r="K100" s="3">
         <v>-134300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>313600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>255400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-84600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-562100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>793900</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>58200</v>
+        <v>88600</v>
       </c>
       <c r="E101" s="3">
-        <v>82600</v>
+        <v>55100</v>
       </c>
       <c r="F101" s="3">
-        <v>49500</v>
+        <v>78200</v>
       </c>
       <c r="G101" s="3">
-        <v>-28800</v>
+        <v>46800</v>
       </c>
       <c r="H101" s="3">
-        <v>7400</v>
+        <v>-27300</v>
       </c>
       <c r="I101" s="3">
-        <v>-10000</v>
+        <v>7000</v>
       </c>
       <c r="J101" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="K101" s="3">
         <v>-18700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-62900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>73800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>75800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>64600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-23500</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-155900</v>
+        <v>-263100</v>
       </c>
       <c r="E102" s="3">
-        <v>-649200</v>
+        <v>-147600</v>
       </c>
       <c r="F102" s="3">
-        <v>449300</v>
+        <v>-614500</v>
       </c>
       <c r="G102" s="3">
-        <v>159000</v>
+        <v>425300</v>
       </c>
       <c r="H102" s="3">
-        <v>536000</v>
+        <v>150500</v>
       </c>
       <c r="I102" s="3">
-        <v>230100</v>
+        <v>507400</v>
       </c>
       <c r="J102" s="3">
+        <v>217800</v>
+      </c>
+      <c r="K102" s="3">
         <v>-277100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>219200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-19800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>210600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-356000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-144700</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/RICOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RICOY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
   <si>
     <t>RICOY</t>
   </si>
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>14986500</v>
+        <v>16677800</v>
       </c>
       <c r="E8" s="3">
-        <v>13616100</v>
+        <v>15152700</v>
       </c>
       <c r="F8" s="3">
-        <v>11219800</v>
+        <v>12486000</v>
       </c>
       <c r="G8" s="3">
-        <v>10731600</v>
+        <v>11942700</v>
       </c>
       <c r="H8" s="3">
-        <v>12814700</v>
+        <v>14260900</v>
       </c>
       <c r="I8" s="3">
-        <v>12844400</v>
+        <v>14293900</v>
       </c>
       <c r="J8" s="3">
-        <v>13164300</v>
+        <v>14649900</v>
       </c>
       <c r="K8" s="3">
         <v>13674800</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>9754300</v>
+        <v>10855100</v>
       </c>
       <c r="E9" s="3">
-        <v>8860300</v>
+        <v>9860200</v>
       </c>
       <c r="F9" s="3">
-        <v>7247200</v>
+        <v>8065000</v>
       </c>
       <c r="G9" s="3">
-        <v>7080300</v>
+        <v>7879300</v>
       </c>
       <c r="H9" s="3">
-        <v>8209600</v>
+        <v>9136100</v>
       </c>
       <c r="I9" s="3">
-        <v>7951700</v>
+        <v>8849000</v>
       </c>
       <c r="J9" s="3">
-        <v>8117600</v>
+        <v>9033700</v>
       </c>
       <c r="K9" s="3">
         <v>8359400</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>5232200</v>
+        <v>5822700</v>
       </c>
       <c r="E10" s="3">
-        <v>4755800</v>
+        <v>5292500</v>
       </c>
       <c r="F10" s="3">
-        <v>3972600</v>
+        <v>4420900</v>
       </c>
       <c r="G10" s="3">
-        <v>3651300</v>
+        <v>4063400</v>
       </c>
       <c r="H10" s="3">
-        <v>4605200</v>
+        <v>5124900</v>
       </c>
       <c r="I10" s="3">
-        <v>4892700</v>
+        <v>5444900</v>
       </c>
       <c r="J10" s="3">
-        <v>5046600</v>
+        <v>5616100</v>
       </c>
       <c r="K10" s="3">
         <v>5315400</v>
@@ -879,26 +879,26 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>10</v>
+      <c r="D12" s="3">
+        <v>677100</v>
       </c>
       <c r="E12" s="3">
-        <v>544300</v>
+        <v>605700</v>
       </c>
       <c r="F12" s="3">
-        <v>483100</v>
+        <v>537600</v>
       </c>
       <c r="G12" s="3">
-        <v>505300</v>
+        <v>562300</v>
       </c>
       <c r="H12" s="3">
-        <v>562900</v>
+        <v>626400</v>
       </c>
       <c r="I12" s="3">
-        <v>599900</v>
+        <v>667600</v>
       </c>
       <c r="J12" s="3">
-        <v>599600</v>
+        <v>667300</v>
       </c>
       <c r="K12" s="3">
         <v>676600</v>
@@ -970,25 +970,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>3900</v>
+        <v>4800</v>
       </c>
       <c r="E14" s="3">
-        <v>-4500</v>
+        <v>-5000</v>
       </c>
       <c r="F14" s="3">
-        <v>12900</v>
+        <v>14400</v>
       </c>
       <c r="G14" s="3">
-        <v>317600</v>
+        <v>353400</v>
       </c>
       <c r="H14" s="3">
-        <v>71800</v>
+        <v>79900</v>
       </c>
       <c r="I14" s="3">
-        <v>136700</v>
+        <v>152100</v>
       </c>
       <c r="J14" s="3">
-        <v>1286900</v>
+        <v>1432200</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>10</v>
@@ -1014,26 +1014,26 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>10</v>
+      <c r="D15" s="3">
+        <v>431300</v>
       </c>
       <c r="E15" s="3">
-        <v>362000</v>
+        <v>402800</v>
       </c>
       <c r="F15" s="3">
-        <v>321100</v>
+        <v>357400</v>
       </c>
       <c r="G15" s="3">
-        <v>347200</v>
+        <v>386400</v>
       </c>
       <c r="H15" s="3">
-        <v>340300</v>
+        <v>378700</v>
       </c>
       <c r="I15" s="3">
-        <v>158600</v>
+        <v>176500</v>
       </c>
       <c r="J15" s="3">
-        <v>255800</v>
+        <v>284700</v>
       </c>
       <c r="K15" s="3">
         <v>271500</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>14590800</v>
+        <v>16237400</v>
       </c>
       <c r="E17" s="3">
-        <v>13113700</v>
+        <v>14593600</v>
       </c>
       <c r="F17" s="3">
-        <v>10964300</v>
+        <v>12201600</v>
       </c>
       <c r="G17" s="3">
-        <v>11021400</v>
+        <v>12265200</v>
       </c>
       <c r="H17" s="3">
-        <v>12310500</v>
+        <v>13699700</v>
       </c>
       <c r="I17" s="3">
-        <v>12290400</v>
+        <v>13677400</v>
       </c>
       <c r="J17" s="3">
-        <v>13902300</v>
+        <v>15471200</v>
       </c>
       <c r="K17" s="3">
         <v>13446400</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>395700</v>
+        <v>440400</v>
       </c>
       <c r="E18" s="3">
-        <v>502400</v>
+        <v>559100</v>
       </c>
       <c r="F18" s="3">
-        <v>255500</v>
+        <v>284400</v>
       </c>
       <c r="G18" s="3">
-        <v>-289800</v>
+        <v>-322500</v>
       </c>
       <c r="H18" s="3">
-        <v>504300</v>
+        <v>561200</v>
       </c>
       <c r="I18" s="3">
-        <v>554000</v>
+        <v>616600</v>
       </c>
       <c r="J18" s="3">
-        <v>-738000</v>
+        <v>-821300</v>
       </c>
       <c r="K18" s="3">
         <v>228400</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>39400</v>
+        <v>83000</v>
       </c>
       <c r="E20" s="3">
-        <v>54800</v>
+        <v>60900</v>
       </c>
       <c r="F20" s="3">
-        <v>48500</v>
+        <v>53900</v>
       </c>
       <c r="G20" s="3">
-        <v>47500</v>
+        <v>52900</v>
       </c>
       <c r="H20" s="3">
-        <v>16700</v>
+        <v>18600</v>
       </c>
       <c r="I20" s="3">
-        <v>19700</v>
+        <v>21900</v>
       </c>
       <c r="J20" s="3">
-        <v>-11400</v>
+        <v>-12600</v>
       </c>
       <c r="K20" s="3">
         <v>24400</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1129600</v>
+        <v>1292000</v>
       </c>
       <c r="E21" s="3">
-        <v>1178000</v>
+        <v>1307100</v>
       </c>
       <c r="F21" s="3">
-        <v>880300</v>
+        <v>976200</v>
       </c>
       <c r="G21" s="3">
-        <v>424100</v>
+        <v>467900</v>
       </c>
       <c r="H21" s="3">
-        <v>1289800</v>
+        <v>1430600</v>
       </c>
       <c r="I21" s="3">
-        <v>1174400</v>
+        <v>1303200</v>
       </c>
       <c r="J21" s="3">
-        <v>-59300</v>
+        <v>-70200</v>
       </c>
       <c r="K21" s="3">
         <v>976400</v>
@@ -1274,26 +1274,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>10</v>
+      <c r="D22" s="3">
+        <v>39100</v>
       </c>
       <c r="E22" s="3">
-        <v>38400</v>
+        <v>42700</v>
       </c>
       <c r="F22" s="3">
-        <v>20800</v>
+        <v>23100</v>
       </c>
       <c r="G22" s="3">
-        <v>19400</v>
+        <v>21600</v>
       </c>
       <c r="H22" s="3">
-        <v>36800</v>
+        <v>41000</v>
       </c>
       <c r="I22" s="3">
-        <v>38100</v>
+        <v>42300</v>
       </c>
       <c r="J22" s="3">
-        <v>42900</v>
+        <v>47800</v>
       </c>
       <c r="K22" s="3">
         <v>50900</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>435100</v>
+        <v>484200</v>
       </c>
       <c r="E23" s="3">
-        <v>518700</v>
+        <v>577300</v>
       </c>
       <c r="F23" s="3">
-        <v>283200</v>
+        <v>315200</v>
       </c>
       <c r="G23" s="3">
-        <v>-261800</v>
+        <v>-291300</v>
       </c>
       <c r="H23" s="3">
-        <v>484200</v>
+        <v>538800</v>
       </c>
       <c r="I23" s="3">
-        <v>535700</v>
+        <v>596100</v>
       </c>
       <c r="J23" s="3">
-        <v>-792300</v>
+        <v>-881700</v>
       </c>
       <c r="K23" s="3">
         <v>201900</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>152900</v>
+        <v>170100</v>
       </c>
       <c r="E24" s="3">
-        <v>163800</v>
+        <v>182200</v>
       </c>
       <c r="F24" s="3">
-        <v>87800</v>
+        <v>97700</v>
       </c>
       <c r="G24" s="3">
-        <v>-53400</v>
+        <v>-59400</v>
       </c>
       <c r="H24" s="3">
-        <v>200800</v>
+        <v>223500</v>
       </c>
       <c r="I24" s="3">
-        <v>182400</v>
+        <v>203000</v>
       </c>
       <c r="J24" s="3">
-        <v>26400</v>
+        <v>29400</v>
       </c>
       <c r="K24" s="3">
         <v>138300</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>282300</v>
+        <v>314100</v>
       </c>
       <c r="E26" s="3">
-        <v>355000</v>
+        <v>395100</v>
       </c>
       <c r="F26" s="3">
-        <v>195400</v>
+        <v>217400</v>
       </c>
       <c r="G26" s="3">
-        <v>-208400</v>
+        <v>-231900</v>
       </c>
       <c r="H26" s="3">
-        <v>283400</v>
+        <v>315300</v>
       </c>
       <c r="I26" s="3">
-        <v>353300</v>
+        <v>393200</v>
       </c>
       <c r="J26" s="3">
-        <v>-818700</v>
+        <v>-911100</v>
       </c>
       <c r="K26" s="3">
         <v>63600</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>281800</v>
+        <v>313600</v>
       </c>
       <c r="E27" s="3">
-        <v>346900</v>
+        <v>386000</v>
       </c>
       <c r="F27" s="3">
-        <v>193800</v>
+        <v>215600</v>
       </c>
       <c r="G27" s="3">
-        <v>-208800</v>
+        <v>-232400</v>
       </c>
       <c r="H27" s="3">
-        <v>252300</v>
+        <v>280800</v>
       </c>
       <c r="I27" s="3">
-        <v>316000</v>
+        <v>351600</v>
       </c>
       <c r="J27" s="3">
-        <v>-855300</v>
+        <v>-951800</v>
       </c>
       <c r="K27" s="3">
         <v>23500</v>
@@ -1608,7 +1608,7 @@
         <v>10</v>
       </c>
       <c r="J29" s="3">
-        <v>-8400</v>
+        <v>-9300</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>10</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-39400</v>
+        <v>-83000</v>
       </c>
       <c r="E32" s="3">
-        <v>-54800</v>
+        <v>-60900</v>
       </c>
       <c r="F32" s="3">
-        <v>-48500</v>
+        <v>-53900</v>
       </c>
       <c r="G32" s="3">
-        <v>-47500</v>
+        <v>-52900</v>
       </c>
       <c r="H32" s="3">
-        <v>-16700</v>
+        <v>-18600</v>
       </c>
       <c r="I32" s="3">
-        <v>-19700</v>
+        <v>-21900</v>
       </c>
       <c r="J32" s="3">
-        <v>11400</v>
+        <v>12600</v>
       </c>
       <c r="K32" s="3">
         <v>-24400</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>281800</v>
+        <v>313600</v>
       </c>
       <c r="E33" s="3">
-        <v>346900</v>
+        <v>386000</v>
       </c>
       <c r="F33" s="3">
-        <v>193800</v>
+        <v>215600</v>
       </c>
       <c r="G33" s="3">
-        <v>-208800</v>
+        <v>-232400</v>
       </c>
       <c r="H33" s="3">
-        <v>252300</v>
+        <v>280800</v>
       </c>
       <c r="I33" s="3">
-        <v>316000</v>
+        <v>351600</v>
       </c>
       <c r="J33" s="3">
-        <v>-863700</v>
+        <v>-961100</v>
       </c>
       <c r="K33" s="3">
         <v>23500</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>281800</v>
+        <v>313600</v>
       </c>
       <c r="E35" s="3">
-        <v>346900</v>
+        <v>386000</v>
       </c>
       <c r="F35" s="3">
-        <v>193800</v>
+        <v>215600</v>
       </c>
       <c r="G35" s="3">
-        <v>-208800</v>
+        <v>-232400</v>
       </c>
       <c r="H35" s="3">
-        <v>252300</v>
+        <v>280800</v>
       </c>
       <c r="I35" s="3">
-        <v>316000</v>
+        <v>351600</v>
       </c>
       <c r="J35" s="3">
-        <v>-863700</v>
+        <v>-961100</v>
       </c>
       <c r="K35" s="3">
         <v>23500</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1129600</v>
+        <v>1257100</v>
       </c>
       <c r="E41" s="3">
-        <v>1415700</v>
+        <v>1575400</v>
       </c>
       <c r="F41" s="3">
-        <v>1533200</v>
+        <v>1706200</v>
       </c>
       <c r="G41" s="3">
-        <v>2136100</v>
+        <v>2377200</v>
       </c>
       <c r="H41" s="3">
-        <v>1676900</v>
+        <v>1866100</v>
       </c>
       <c r="I41" s="3">
-        <v>1531800</v>
+        <v>1704700</v>
       </c>
       <c r="J41" s="3">
-        <v>1024400</v>
+        <v>1140000</v>
       </c>
       <c r="K41" s="3">
         <v>852100</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>684100</v>
+        <v>761300</v>
       </c>
       <c r="E42" s="3">
-        <v>600400</v>
+        <v>668200</v>
       </c>
       <c r="F42" s="3">
-        <v>589300</v>
+        <v>655900</v>
       </c>
       <c r="G42" s="3">
-        <v>593700</v>
+        <v>660700</v>
       </c>
       <c r="H42" s="3">
-        <v>556800</v>
+        <v>619700</v>
       </c>
       <c r="I42" s="3">
-        <v>1878400</v>
+        <v>2090400</v>
       </c>
       <c r="J42" s="3">
-        <v>2214700</v>
+        <v>2464600</v>
       </c>
       <c r="K42" s="3">
         <v>1922500</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3432800</v>
+        <v>3820200</v>
       </c>
       <c r="E43" s="3">
-        <v>3039600</v>
+        <v>3382600</v>
       </c>
       <c r="F43" s="3">
-        <v>2533800</v>
+        <v>2819800</v>
       </c>
       <c r="G43" s="3">
-        <v>2501800</v>
+        <v>2784100</v>
       </c>
       <c r="H43" s="3">
-        <v>2505900</v>
+        <v>2788700</v>
       </c>
       <c r="I43" s="3">
-        <v>3858600</v>
+        <v>4294100</v>
       </c>
       <c r="J43" s="3">
-        <v>3762500</v>
+        <v>4187200</v>
       </c>
       <c r="K43" s="3">
         <v>3817000</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1917800</v>
+        <v>2134200</v>
       </c>
       <c r="E44" s="3">
-        <v>2005700</v>
+        <v>2232000</v>
       </c>
       <c r="F44" s="3">
-        <v>1483700</v>
+        <v>1651200</v>
       </c>
       <c r="G44" s="3">
-        <v>1225100</v>
+        <v>1363300</v>
       </c>
       <c r="H44" s="3">
-        <v>1284000</v>
+        <v>1428900</v>
       </c>
       <c r="I44" s="3">
-        <v>1325400</v>
+        <v>1475000</v>
       </c>
       <c r="J44" s="3">
-        <v>1151500</v>
+        <v>1281400</v>
       </c>
       <c r="K44" s="3">
         <v>1365200</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>512800</v>
+        <v>570700</v>
       </c>
       <c r="E45" s="3">
-        <v>437000</v>
+        <v>486300</v>
       </c>
       <c r="F45" s="3">
-        <v>319200</v>
+        <v>355200</v>
       </c>
       <c r="G45" s="3">
-        <v>298100</v>
+        <v>331700</v>
       </c>
       <c r="H45" s="3">
-        <v>7413600</v>
+        <v>8250300</v>
       </c>
       <c r="I45" s="3">
-        <v>272400</v>
+        <v>303100</v>
       </c>
       <c r="J45" s="3">
-        <v>319300</v>
+        <v>355400</v>
       </c>
       <c r="K45" s="3">
         <v>395500</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>7677100</v>
+        <v>8543400</v>
       </c>
       <c r="E46" s="3">
-        <v>7498400</v>
+        <v>8344600</v>
       </c>
       <c r="F46" s="3">
-        <v>6459300</v>
+        <v>7188200</v>
       </c>
       <c r="G46" s="3">
-        <v>6754800</v>
+        <v>7517100</v>
       </c>
       <c r="H46" s="3">
-        <v>13437200</v>
+        <v>14953700</v>
       </c>
       <c r="I46" s="3">
-        <v>8866700</v>
+        <v>9867300</v>
       </c>
       <c r="J46" s="3">
-        <v>8472500</v>
+        <v>9428600</v>
       </c>
       <c r="K46" s="3">
         <v>8352300</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1752600</v>
+        <v>1950400</v>
       </c>
       <c r="E47" s="3">
-        <v>1518700</v>
+        <v>1690100</v>
       </c>
       <c r="F47" s="3">
-        <v>1416700</v>
+        <v>1576500</v>
       </c>
       <c r="G47" s="3">
-        <v>1493600</v>
+        <v>1662100</v>
       </c>
       <c r="H47" s="3">
-        <v>1074600</v>
+        <v>1195900</v>
       </c>
       <c r="I47" s="3">
-        <v>4742000</v>
+        <v>5277100</v>
       </c>
       <c r="J47" s="3">
-        <v>4595600</v>
+        <v>5114300</v>
       </c>
       <c r="K47" s="3">
         <v>4972400</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1698800</v>
+        <v>1890500</v>
       </c>
       <c r="E48" s="3">
-        <v>1617400</v>
+        <v>1800000</v>
       </c>
       <c r="F48" s="3">
-        <v>1570600</v>
+        <v>1747800</v>
       </c>
       <c r="G48" s="3">
-        <v>1630800</v>
+        <v>1814900</v>
       </c>
       <c r="H48" s="3">
-        <v>1665100</v>
+        <v>1853100</v>
       </c>
       <c r="I48" s="3">
-        <v>1596800</v>
+        <v>1777000</v>
       </c>
       <c r="J48" s="3">
-        <v>1595000</v>
+        <v>1775000</v>
       </c>
       <c r="K48" s="3">
         <v>1828300</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2631500</v>
+        <v>2928500</v>
       </c>
       <c r="E49" s="3">
-        <v>2337600</v>
+        <v>2601400</v>
       </c>
       <c r="F49" s="3">
-        <v>1655500</v>
+        <v>1842300</v>
       </c>
       <c r="G49" s="3">
-        <v>1438800</v>
+        <v>1601100</v>
       </c>
       <c r="H49" s="3">
-        <v>1479500</v>
+        <v>1646500</v>
       </c>
       <c r="I49" s="3">
-        <v>1402400</v>
+        <v>1560600</v>
       </c>
       <c r="J49" s="3">
-        <v>1385300</v>
+        <v>1541600</v>
       </c>
       <c r="K49" s="3">
         <v>2616300</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>825800</v>
+        <v>919000</v>
       </c>
       <c r="E52" s="3">
-        <v>744600</v>
+        <v>828600</v>
       </c>
       <c r="F52" s="3">
-        <v>721800</v>
+        <v>803300</v>
       </c>
       <c r="G52" s="3">
-        <v>726700</v>
+        <v>808700</v>
       </c>
       <c r="H52" s="3">
-        <v>639100</v>
+        <v>711200</v>
       </c>
       <c r="I52" s="3">
-        <v>778500</v>
+        <v>866300</v>
       </c>
       <c r="J52" s="3">
-        <v>801300</v>
+        <v>891800</v>
       </c>
       <c r="K52" s="3">
         <v>828300</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>14585800</v>
+        <v>16231800</v>
       </c>
       <c r="E54" s="3">
-        <v>13716700</v>
+        <v>15264700</v>
       </c>
       <c r="F54" s="3">
-        <v>11823800</v>
+        <v>13158100</v>
       </c>
       <c r="G54" s="3">
-        <v>12044600</v>
+        <v>13403900</v>
       </c>
       <c r="H54" s="3">
-        <v>18295600</v>
+        <v>20360300</v>
       </c>
       <c r="I54" s="3">
-        <v>17386300</v>
+        <v>19348400</v>
       </c>
       <c r="J54" s="3">
-        <v>16849800</v>
+        <v>18751300</v>
       </c>
       <c r="K54" s="3">
         <v>18597600</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1947700</v>
+        <v>1678100</v>
       </c>
       <c r="E57" s="3">
-        <v>1391400</v>
+        <v>1548400</v>
       </c>
       <c r="F57" s="3">
-        <v>1131600</v>
+        <v>1259400</v>
       </c>
       <c r="G57" s="3">
-        <v>1283600</v>
+        <v>1428500</v>
       </c>
       <c r="H57" s="3">
-        <v>1144800</v>
+        <v>1274000</v>
       </c>
       <c r="I57" s="3">
-        <v>1328500</v>
+        <v>1478500</v>
       </c>
       <c r="J57" s="3">
-        <v>1240400</v>
+        <v>1380300</v>
       </c>
       <c r="K57" s="3">
         <v>1315800</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1117400</v>
+        <v>1243500</v>
       </c>
       <c r="E58" s="3">
-        <v>1174000</v>
+        <v>1306500</v>
       </c>
       <c r="F58" s="3">
-        <v>874400</v>
+        <v>973100</v>
       </c>
       <c r="G58" s="3">
-        <v>690400</v>
+        <v>768300</v>
       </c>
       <c r="H58" s="3">
-        <v>502200</v>
+        <v>558900</v>
       </c>
       <c r="I58" s="3">
-        <v>1703200</v>
+        <v>1895400</v>
       </c>
       <c r="J58" s="3">
-        <v>1424000</v>
+        <v>1584700</v>
       </c>
       <c r="K58" s="3">
         <v>1549800</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2544700</v>
+        <v>3321300</v>
       </c>
       <c r="E59" s="3">
-        <v>2724400</v>
+        <v>3031800</v>
       </c>
       <c r="F59" s="3">
-        <v>2418100</v>
+        <v>2691000</v>
       </c>
       <c r="G59" s="3">
-        <v>2221000</v>
+        <v>2471600</v>
       </c>
       <c r="H59" s="3">
-        <v>8234900</v>
+        <v>9164300</v>
       </c>
       <c r="I59" s="3">
-        <v>2354300</v>
+        <v>2619900</v>
       </c>
       <c r="J59" s="3">
-        <v>2366400</v>
+        <v>2633500</v>
       </c>
       <c r="K59" s="3">
         <v>2573000</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>5609800</v>
+        <v>6242900</v>
       </c>
       <c r="E60" s="3">
-        <v>5289700</v>
+        <v>5886700</v>
       </c>
       <c r="F60" s="3">
-        <v>4424200</v>
+        <v>4923500</v>
       </c>
       <c r="G60" s="3">
-        <v>4195000</v>
+        <v>4668400</v>
       </c>
       <c r="H60" s="3">
-        <v>9882000</v>
+        <v>10997200</v>
       </c>
       <c r="I60" s="3">
-        <v>5386000</v>
+        <v>5993800</v>
       </c>
       <c r="J60" s="3">
-        <v>5030800</v>
+        <v>5598500</v>
       </c>
       <c r="K60" s="3">
         <v>5438700</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1562700</v>
+        <v>1739100</v>
       </c>
       <c r="E61" s="3">
-        <v>1552000</v>
+        <v>1727100</v>
       </c>
       <c r="F61" s="3">
-        <v>1055800</v>
+        <v>1175000</v>
       </c>
       <c r="G61" s="3">
-        <v>1189300</v>
+        <v>1323500</v>
       </c>
       <c r="H61" s="3">
-        <v>1064900</v>
+        <v>1185100</v>
       </c>
       <c r="I61" s="3">
-        <v>4252000</v>
+        <v>4731900</v>
       </c>
       <c r="J61" s="3">
-        <v>4202600</v>
+        <v>4676800</v>
       </c>
       <c r="K61" s="3">
         <v>4244800</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>617800</v>
+        <v>687500</v>
       </c>
       <c r="E62" s="3">
-        <v>762400</v>
+        <v>848500</v>
       </c>
       <c r="F62" s="3">
-        <v>564600</v>
+        <v>628300</v>
       </c>
       <c r="G62" s="3">
-        <v>766200</v>
+        <v>852600</v>
       </c>
       <c r="H62" s="3">
-        <v>914300</v>
+        <v>1017500</v>
       </c>
       <c r="I62" s="3">
-        <v>1247200</v>
+        <v>1387900</v>
       </c>
       <c r="J62" s="3">
-        <v>1308200</v>
+        <v>1455800</v>
       </c>
       <c r="K62" s="3">
         <v>1386300</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>7958800</v>
+        <v>8856900</v>
       </c>
       <c r="E66" s="3">
-        <v>7773400</v>
+        <v>8650600</v>
       </c>
       <c r="F66" s="3">
-        <v>6068700</v>
+        <v>6753600</v>
       </c>
       <c r="G66" s="3">
-        <v>6173400</v>
+        <v>6870100</v>
       </c>
       <c r="H66" s="3">
-        <v>12423600</v>
+        <v>13825600</v>
       </c>
       <c r="I66" s="3">
-        <v>11436500</v>
+        <v>12727100</v>
       </c>
       <c r="J66" s="3">
-        <v>11046700</v>
+        <v>12293400</v>
       </c>
       <c r="K66" s="3">
         <v>11573800</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>3197300</v>
+        <v>3558100</v>
       </c>
       <c r="E72" s="3">
-        <v>3003200</v>
+        <v>3342100</v>
       </c>
       <c r="F72" s="3">
-        <v>2933900</v>
+        <v>3265000</v>
       </c>
       <c r="G72" s="3">
-        <v>3582900</v>
+        <v>3987200</v>
       </c>
       <c r="H72" s="3">
-        <v>3794400</v>
+        <v>4222600</v>
       </c>
       <c r="I72" s="3">
-        <v>3667700</v>
+        <v>4081600</v>
       </c>
       <c r="J72" s="3">
-        <v>3254500</v>
+        <v>3621800</v>
       </c>
       <c r="K72" s="3">
         <v>4431200</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>6627000</v>
+        <v>7374900</v>
       </c>
       <c r="E76" s="3">
-        <v>5943300</v>
+        <v>6614000</v>
       </c>
       <c r="F76" s="3">
-        <v>5755000</v>
+        <v>6404500</v>
       </c>
       <c r="G76" s="3">
-        <v>5871200</v>
+        <v>6533700</v>
       </c>
       <c r="H76" s="3">
-        <v>5872000</v>
+        <v>6534600</v>
       </c>
       <c r="I76" s="3">
-        <v>5949800</v>
+        <v>6621300</v>
       </c>
       <c r="J76" s="3">
-        <v>5803000</v>
+        <v>6457900</v>
       </c>
       <c r="K76" s="3">
         <v>7023800</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>281800</v>
+        <v>313600</v>
       </c>
       <c r="E81" s="3">
-        <v>346900</v>
+        <v>386000</v>
       </c>
       <c r="F81" s="3">
-        <v>193800</v>
+        <v>215600</v>
       </c>
       <c r="G81" s="3">
-        <v>-208800</v>
+        <v>-232400</v>
       </c>
       <c r="H81" s="3">
-        <v>252300</v>
+        <v>280800</v>
       </c>
       <c r="I81" s="3">
-        <v>316000</v>
+        <v>351600</v>
       </c>
       <c r="J81" s="3">
-        <v>-863700</v>
+        <v>-961100</v>
       </c>
       <c r="K81" s="3">
         <v>23500</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>695600</v>
+        <v>774100</v>
       </c>
       <c r="E83" s="3">
-        <v>621800</v>
+        <v>692000</v>
       </c>
       <c r="F83" s="3">
-        <v>577300</v>
+        <v>642400</v>
       </c>
       <c r="G83" s="3">
-        <v>667500</v>
+        <v>742800</v>
       </c>
       <c r="H83" s="3">
-        <v>770000</v>
+        <v>856900</v>
       </c>
       <c r="I83" s="3">
-        <v>601600</v>
+        <v>669400</v>
       </c>
       <c r="J83" s="3">
-        <v>691100</v>
+        <v>769100</v>
       </c>
       <c r="K83" s="3">
         <v>720400</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>801400</v>
+        <v>891900</v>
       </c>
       <c r="E89" s="3">
-        <v>425600</v>
+        <v>473600</v>
       </c>
       <c r="F89" s="3">
-        <v>526100</v>
+        <v>585500</v>
       </c>
       <c r="G89" s="3">
-        <v>810000</v>
+        <v>901400</v>
       </c>
       <c r="H89" s="3">
-        <v>744600</v>
+        <v>828600</v>
       </c>
       <c r="I89" s="3">
-        <v>522800</v>
+        <v>581800</v>
       </c>
       <c r="J89" s="3">
-        <v>703600</v>
+        <v>783000</v>
       </c>
       <c r="K89" s="3">
         <v>595100</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-339800</v>
+        <v>-378200</v>
       </c>
       <c r="E91" s="3">
-        <v>-290000</v>
+        <v>-322800</v>
       </c>
       <c r="F91" s="3">
-        <v>-238400</v>
+        <v>-265200</v>
       </c>
       <c r="G91" s="3">
-        <v>-268900</v>
+        <v>-299300</v>
       </c>
       <c r="H91" s="3">
-        <v>-552500</v>
+        <v>-614800</v>
       </c>
       <c r="I91" s="3">
-        <v>-462300</v>
+        <v>-514500</v>
       </c>
       <c r="J91" s="3">
-        <v>-461200</v>
+        <v>-513200</v>
       </c>
       <c r="K91" s="3">
         <v>-508500</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-624100</v>
+        <v>-694500</v>
       </c>
       <c r="E94" s="3">
-        <v>-854500</v>
+        <v>-951000</v>
       </c>
       <c r="F94" s="3">
-        <v>-378700</v>
+        <v>-421400</v>
       </c>
       <c r="G94" s="3">
-        <v>-405500</v>
+        <v>-451300</v>
       </c>
       <c r="H94" s="3">
-        <v>-1050100</v>
+        <v>-1168600</v>
       </c>
       <c r="I94" s="3">
-        <v>-293000</v>
+        <v>-326100</v>
       </c>
       <c r="J94" s="3">
-        <v>-517300</v>
+        <v>-575600</v>
       </c>
       <c r="K94" s="3">
         <v>-719300</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-136000</v>
+        <v>-151400</v>
       </c>
       <c r="E96" s="3">
-        <v>-118900</v>
+        <v>-132300</v>
       </c>
       <c r="F96" s="3">
-        <v>-89700</v>
+        <v>-99800</v>
       </c>
       <c r="G96" s="3">
-        <v>-94700</v>
+        <v>-105400</v>
       </c>
       <c r="H96" s="3">
-        <v>-120200</v>
+        <v>-133800</v>
       </c>
       <c r="I96" s="3">
-        <v>-80900</v>
+        <v>-90100</v>
       </c>
       <c r="J96" s="3">
-        <v>-92500</v>
+        <v>-102900</v>
       </c>
       <c r="K96" s="3">
         <v>-195400</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-529000</v>
+        <v>-588700</v>
       </c>
       <c r="E100" s="3">
-        <v>226200</v>
+        <v>251700</v>
       </c>
       <c r="F100" s="3">
-        <v>-840200</v>
+        <v>-935000</v>
       </c>
       <c r="G100" s="3">
-        <v>-26100</v>
+        <v>-29000</v>
       </c>
       <c r="H100" s="3">
-        <v>483300</v>
+        <v>537900</v>
       </c>
       <c r="I100" s="3">
-        <v>270700</v>
+        <v>301200</v>
       </c>
       <c r="J100" s="3">
-        <v>40900</v>
+        <v>45500</v>
       </c>
       <c r="K100" s="3">
         <v>-134300</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>88600</v>
+        <v>98600</v>
       </c>
       <c r="E101" s="3">
-        <v>55100</v>
+        <v>61400</v>
       </c>
       <c r="F101" s="3">
-        <v>78200</v>
+        <v>87000</v>
       </c>
       <c r="G101" s="3">
-        <v>46800</v>
+        <v>52100</v>
       </c>
       <c r="H101" s="3">
-        <v>-27300</v>
+        <v>-30400</v>
       </c>
       <c r="I101" s="3">
-        <v>7000</v>
+        <v>7700</v>
       </c>
       <c r="J101" s="3">
-        <v>-9400</v>
+        <v>-10500</v>
       </c>
       <c r="K101" s="3">
         <v>-18700</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-263100</v>
+        <v>-292800</v>
       </c>
       <c r="E102" s="3">
-        <v>-147600</v>
+        <v>-164300</v>
       </c>
       <c r="F102" s="3">
-        <v>-614500</v>
+        <v>-683900</v>
       </c>
       <c r="G102" s="3">
-        <v>425300</v>
+        <v>473300</v>
       </c>
       <c r="H102" s="3">
-        <v>150500</v>
+        <v>167500</v>
       </c>
       <c r="I102" s="3">
-        <v>507400</v>
+        <v>564700</v>
       </c>
       <c r="J102" s="3">
-        <v>217800</v>
+        <v>242400</v>
       </c>
       <c r="K102" s="3">
         <v>-277100</v>

--- a/AAII_Financials/Yearly/RICOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RICOY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
   <si>
     <t>RICOY</t>
   </si>
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>16677800</v>
+        <v>15530000</v>
       </c>
       <c r="E8" s="3">
-        <v>15152700</v>
+        <v>16054400</v>
       </c>
       <c r="F8" s="3">
-        <v>12486000</v>
+        <v>14481800</v>
       </c>
       <c r="G8" s="3">
-        <v>11942700</v>
+        <v>15208700</v>
       </c>
       <c r="H8" s="3">
-        <v>14260900</v>
+        <v>18666800</v>
       </c>
       <c r="I8" s="3">
-        <v>14293900</v>
+        <v>18168300</v>
       </c>
       <c r="J8" s="3">
-        <v>14649900</v>
+        <v>19428100</v>
       </c>
       <c r="K8" s="3">
         <v>13674800</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>10855100</v>
+        <v>10108000</v>
       </c>
       <c r="E9" s="3">
-        <v>9860200</v>
+        <v>10447000</v>
       </c>
       <c r="F9" s="3">
-        <v>8065000</v>
+        <v>9354200</v>
       </c>
       <c r="G9" s="3">
-        <v>7879300</v>
+        <v>10034100</v>
       </c>
       <c r="H9" s="3">
-        <v>9136100</v>
+        <v>11960800</v>
       </c>
       <c r="I9" s="3">
-        <v>8849000</v>
+        <v>11247600</v>
       </c>
       <c r="J9" s="3">
-        <v>9033700</v>
+        <v>11980200</v>
       </c>
       <c r="K9" s="3">
         <v>8359400</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>5822700</v>
+        <v>5422000</v>
       </c>
       <c r="E10" s="3">
-        <v>5292500</v>
+        <v>5607500</v>
       </c>
       <c r="F10" s="3">
-        <v>4420900</v>
+        <v>5127600</v>
       </c>
       <c r="G10" s="3">
-        <v>4063400</v>
+        <v>5174600</v>
       </c>
       <c r="H10" s="3">
-        <v>5124900</v>
+        <v>6706000</v>
       </c>
       <c r="I10" s="3">
-        <v>5444900</v>
+        <v>6920700</v>
       </c>
       <c r="J10" s="3">
-        <v>5616100</v>
+        <v>7447900</v>
       </c>
       <c r="K10" s="3">
         <v>5315400</v>
@@ -880,25 +880,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>677100</v>
+        <v>692100</v>
       </c>
       <c r="E12" s="3">
-        <v>605700</v>
+        <v>688600</v>
       </c>
       <c r="F12" s="3">
-        <v>537600</v>
+        <v>796500</v>
       </c>
       <c r="G12" s="3">
-        <v>562300</v>
+        <v>716000</v>
       </c>
       <c r="H12" s="3">
-        <v>626400</v>
+        <v>819900</v>
       </c>
       <c r="I12" s="3">
-        <v>667600</v>
+        <v>848500</v>
       </c>
       <c r="J12" s="3">
-        <v>667300</v>
+        <v>885000</v>
       </c>
       <c r="K12" s="3">
         <v>676600</v>
@@ -970,25 +970,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>4800</v>
+        <v>-9600</v>
       </c>
       <c r="E14" s="3">
-        <v>-5000</v>
+        <v>-100600</v>
       </c>
       <c r="F14" s="3">
-        <v>14400</v>
+        <v>-112800</v>
       </c>
       <c r="G14" s="3">
-        <v>353400</v>
+        <v>21400</v>
       </c>
       <c r="H14" s="3">
-        <v>79900</v>
+        <v>-57500</v>
       </c>
       <c r="I14" s="3">
-        <v>152100</v>
+        <v>-178400</v>
       </c>
       <c r="J14" s="3">
-        <v>1432200</v>
+        <v>1266000</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>10</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>431300</v>
+        <v>401600</v>
       </c>
       <c r="E15" s="3">
-        <v>402800</v>
+        <v>426800</v>
       </c>
       <c r="F15" s="3">
-        <v>357400</v>
+        <v>414500</v>
       </c>
       <c r="G15" s="3">
-        <v>386400</v>
+        <v>492100</v>
       </c>
       <c r="H15" s="3">
-        <v>378700</v>
+        <v>495700</v>
       </c>
       <c r="I15" s="3">
-        <v>176500</v>
+        <v>224400</v>
       </c>
       <c r="J15" s="3">
-        <v>284700</v>
+        <v>377500</v>
       </c>
       <c r="K15" s="3">
         <v>271500</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>16237400</v>
+        <v>15129500</v>
       </c>
       <c r="E17" s="3">
-        <v>14593600</v>
+        <v>15562700</v>
       </c>
       <c r="F17" s="3">
-        <v>12201600</v>
+        <v>14274200</v>
       </c>
       <c r="G17" s="3">
-        <v>12265200</v>
+        <v>15610400</v>
       </c>
       <c r="H17" s="3">
-        <v>13699700</v>
+        <v>17989700</v>
       </c>
       <c r="I17" s="3">
-        <v>13677400</v>
+        <v>17563000</v>
       </c>
       <c r="J17" s="3">
-        <v>15471200</v>
+        <v>19250300</v>
       </c>
       <c r="K17" s="3">
         <v>13446400</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>440400</v>
+        <v>400500</v>
       </c>
       <c r="E18" s="3">
-        <v>559100</v>
+        <v>491700</v>
       </c>
       <c r="F18" s="3">
-        <v>284400</v>
+        <v>207600</v>
       </c>
       <c r="G18" s="3">
-        <v>-322500</v>
+        <v>-401600</v>
       </c>
       <c r="H18" s="3">
-        <v>561200</v>
+        <v>677100</v>
       </c>
       <c r="I18" s="3">
-        <v>616600</v>
+        <v>605200</v>
       </c>
       <c r="J18" s="3">
-        <v>-821300</v>
+        <v>177800</v>
       </c>
       <c r="K18" s="3">
         <v>228400</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>83000</v>
+        <v>-39900</v>
       </c>
       <c r="E20" s="3">
-        <v>60900</v>
+        <v>-31300</v>
       </c>
       <c r="F20" s="3">
-        <v>53900</v>
+        <v>-54600</v>
       </c>
       <c r="G20" s="3">
-        <v>52900</v>
+        <v>-60300</v>
       </c>
       <c r="H20" s="3">
-        <v>18600</v>
+        <v>18000</v>
       </c>
       <c r="I20" s="3">
-        <v>21900</v>
+        <v>9300</v>
       </c>
       <c r="J20" s="3">
-        <v>-12600</v>
+        <v>54500</v>
       </c>
       <c r="K20" s="3">
         <v>24400</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1292000</v>
+        <v>842000</v>
       </c>
       <c r="E21" s="3">
-        <v>1307100</v>
+        <v>949800</v>
       </c>
       <c r="F21" s="3">
-        <v>976200</v>
+        <v>676700</v>
       </c>
       <c r="G21" s="3">
-        <v>467900</v>
+        <v>150700</v>
       </c>
       <c r="H21" s="3">
-        <v>1430600</v>
+        <v>1154800</v>
       </c>
       <c r="I21" s="3">
-        <v>1303200</v>
+        <v>820300</v>
       </c>
       <c r="J21" s="3">
-        <v>-70200</v>
+        <v>500800</v>
       </c>
       <c r="K21" s="3">
         <v>976400</v>
@@ -1275,25 +1275,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>39100</v>
+        <v>36400</v>
       </c>
       <c r="E22" s="3">
-        <v>42700</v>
+        <v>45200</v>
       </c>
       <c r="F22" s="3">
-        <v>23100</v>
+        <v>26800</v>
       </c>
       <c r="G22" s="3">
-        <v>21600</v>
+        <v>27500</v>
       </c>
       <c r="H22" s="3">
-        <v>41000</v>
+        <v>53600</v>
       </c>
       <c r="I22" s="3">
-        <v>42300</v>
+        <v>53800</v>
       </c>
       <c r="J22" s="3">
-        <v>47800</v>
+        <v>63300</v>
       </c>
       <c r="K22" s="3">
         <v>50900</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>484200</v>
+        <v>450900</v>
       </c>
       <c r="E23" s="3">
-        <v>577300</v>
+        <v>611600</v>
       </c>
       <c r="F23" s="3">
-        <v>315200</v>
+        <v>365500</v>
       </c>
       <c r="G23" s="3">
-        <v>-291300</v>
+        <v>-371000</v>
       </c>
       <c r="H23" s="3">
-        <v>538800</v>
+        <v>705300</v>
       </c>
       <c r="I23" s="3">
-        <v>596100</v>
+        <v>757700</v>
       </c>
       <c r="J23" s="3">
-        <v>-881700</v>
+        <v>-1169300</v>
       </c>
       <c r="K23" s="3">
         <v>201900</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>170100</v>
+        <v>158400</v>
       </c>
       <c r="E24" s="3">
-        <v>182200</v>
+        <v>193100</v>
       </c>
       <c r="F24" s="3">
-        <v>97700</v>
+        <v>113300</v>
       </c>
       <c r="G24" s="3">
-        <v>-59400</v>
+        <v>-75600</v>
       </c>
       <c r="H24" s="3">
-        <v>223500</v>
+        <v>292500</v>
       </c>
       <c r="I24" s="3">
-        <v>203000</v>
+        <v>258000</v>
       </c>
       <c r="J24" s="3">
-        <v>29400</v>
+        <v>51400</v>
       </c>
       <c r="K24" s="3">
         <v>138300</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>314100</v>
+        <v>292500</v>
       </c>
       <c r="E26" s="3">
-        <v>395100</v>
+        <v>418600</v>
       </c>
       <c r="F26" s="3">
-        <v>217400</v>
+        <v>252200</v>
       </c>
       <c r="G26" s="3">
-        <v>-231900</v>
+        <v>-295300</v>
       </c>
       <c r="H26" s="3">
-        <v>315300</v>
+        <v>412800</v>
       </c>
       <c r="I26" s="3">
-        <v>393200</v>
+        <v>499700</v>
       </c>
       <c r="J26" s="3">
-        <v>-911100</v>
+        <v>-1220600</v>
       </c>
       <c r="K26" s="3">
         <v>63600</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>313600</v>
+        <v>292100</v>
       </c>
       <c r="E27" s="3">
-        <v>386000</v>
+        <v>409000</v>
       </c>
       <c r="F27" s="3">
-        <v>215600</v>
+        <v>250100</v>
       </c>
       <c r="G27" s="3">
-        <v>-232400</v>
+        <v>-295900</v>
       </c>
       <c r="H27" s="3">
-        <v>280800</v>
+        <v>367500</v>
       </c>
       <c r="I27" s="3">
-        <v>351600</v>
+        <v>446900</v>
       </c>
       <c r="J27" s="3">
-        <v>-951800</v>
+        <v>-1274600</v>
       </c>
       <c r="K27" s="3">
         <v>23500</v>
@@ -1589,26 +1589,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>10</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-9300</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>10</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-83000</v>
+        <v>39900</v>
       </c>
       <c r="E32" s="3">
-        <v>-60900</v>
+        <v>31300</v>
       </c>
       <c r="F32" s="3">
-        <v>-53900</v>
+        <v>54600</v>
       </c>
       <c r="G32" s="3">
-        <v>-52900</v>
+        <v>60300</v>
       </c>
       <c r="H32" s="3">
-        <v>-18600</v>
+        <v>-18000</v>
       </c>
       <c r="I32" s="3">
-        <v>-21900</v>
+        <v>-9300</v>
       </c>
       <c r="J32" s="3">
-        <v>12600</v>
+        <v>-54500</v>
       </c>
       <c r="K32" s="3">
         <v>-24400</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>313600</v>
+        <v>292100</v>
       </c>
       <c r="E33" s="3">
-        <v>386000</v>
+        <v>409000</v>
       </c>
       <c r="F33" s="3">
-        <v>215600</v>
+        <v>250100</v>
       </c>
       <c r="G33" s="3">
-        <v>-232400</v>
+        <v>-295900</v>
       </c>
       <c r="H33" s="3">
-        <v>280800</v>
+        <v>367500</v>
       </c>
       <c r="I33" s="3">
-        <v>351600</v>
+        <v>446900</v>
       </c>
       <c r="J33" s="3">
-        <v>-961100</v>
+        <v>-1274600</v>
       </c>
       <c r="K33" s="3">
         <v>23500</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>313600</v>
+        <v>292100</v>
       </c>
       <c r="E35" s="3">
-        <v>386000</v>
+        <v>409000</v>
       </c>
       <c r="F35" s="3">
-        <v>215600</v>
+        <v>250100</v>
       </c>
       <c r="G35" s="3">
-        <v>-232400</v>
+        <v>-295900</v>
       </c>
       <c r="H35" s="3">
-        <v>280800</v>
+        <v>367500</v>
       </c>
       <c r="I35" s="3">
-        <v>351600</v>
+        <v>446900</v>
       </c>
       <c r="J35" s="3">
-        <v>-961100</v>
+        <v>-1274600</v>
       </c>
       <c r="K35" s="3">
         <v>23500</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1257100</v>
+        <v>1170500</v>
       </c>
       <c r="E41" s="3">
-        <v>1575400</v>
+        <v>1669200</v>
       </c>
       <c r="F41" s="3">
-        <v>1706200</v>
+        <v>1979600</v>
       </c>
       <c r="G41" s="3">
-        <v>2377200</v>
+        <v>3029400</v>
       </c>
       <c r="H41" s="3">
-        <v>1866100</v>
+        <v>2443100</v>
       </c>
       <c r="I41" s="3">
-        <v>1704700</v>
+        <v>2167400</v>
       </c>
       <c r="J41" s="3">
-        <v>1140000</v>
+        <v>1512500</v>
       </c>
       <c r="K41" s="3">
         <v>852100</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>761300</v>
+        <v>1800</v>
       </c>
       <c r="E42" s="3">
-        <v>668200</v>
+        <v>1600</v>
       </c>
       <c r="F42" s="3">
-        <v>655900</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>660700</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>619700</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>2090400</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>2464600</v>
+        <v>526500</v>
       </c>
       <c r="K42" s="3">
         <v>1922500</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3820200</v>
+        <v>3557300</v>
       </c>
       <c r="E43" s="3">
-        <v>3382600</v>
+        <v>3584000</v>
       </c>
       <c r="F43" s="3">
-        <v>2819800</v>
+        <v>3270500</v>
       </c>
       <c r="G43" s="3">
-        <v>2784100</v>
+        <v>3545500</v>
       </c>
       <c r="H43" s="3">
-        <v>2788700</v>
+        <v>3650300</v>
       </c>
       <c r="I43" s="3">
-        <v>4294100</v>
+        <v>5458000</v>
       </c>
       <c r="J43" s="3">
-        <v>4187200</v>
+        <v>5552900</v>
       </c>
       <c r="K43" s="3">
         <v>3817000</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>2134200</v>
+        <v>1987300</v>
       </c>
       <c r="E44" s="3">
-        <v>2232000</v>
+        <v>2364800</v>
       </c>
       <c r="F44" s="3">
-        <v>1651200</v>
+        <v>1915100</v>
       </c>
       <c r="G44" s="3">
-        <v>1363300</v>
+        <v>1736100</v>
       </c>
       <c r="H44" s="3">
-        <v>1428900</v>
+        <v>1870300</v>
       </c>
       <c r="I44" s="3">
-        <v>1475000</v>
+        <v>1874800</v>
       </c>
       <c r="J44" s="3">
-        <v>1281400</v>
+        <v>1699400</v>
       </c>
       <c r="K44" s="3">
         <v>1365200</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>570700</v>
+        <v>1238500</v>
       </c>
       <c r="E45" s="3">
-        <v>486300</v>
+        <v>1221700</v>
       </c>
       <c r="F45" s="3">
-        <v>355200</v>
+        <v>1172100</v>
       </c>
       <c r="G45" s="3">
-        <v>331700</v>
+        <v>1261700</v>
       </c>
       <c r="H45" s="3">
-        <v>8250300</v>
+        <v>11609800</v>
       </c>
       <c r="I45" s="3">
-        <v>303100</v>
+        <v>3041600</v>
       </c>
       <c r="J45" s="3">
-        <v>355400</v>
+        <v>3212600</v>
       </c>
       <c r="K45" s="3">
         <v>395500</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>8543400</v>
+        <v>7955400</v>
       </c>
       <c r="E46" s="3">
-        <v>8344600</v>
+        <v>8841200</v>
       </c>
       <c r="F46" s="3">
-        <v>7188200</v>
+        <v>8337200</v>
       </c>
       <c r="G46" s="3">
-        <v>7517100</v>
+        <v>9572800</v>
       </c>
       <c r="H46" s="3">
-        <v>14953700</v>
+        <v>19573500</v>
       </c>
       <c r="I46" s="3">
-        <v>9867300</v>
+        <v>12541800</v>
       </c>
       <c r="J46" s="3">
-        <v>9428600</v>
+        <v>12503900</v>
       </c>
       <c r="K46" s="3">
         <v>8352300</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1950400</v>
+        <v>694600</v>
       </c>
       <c r="E47" s="3">
-        <v>1690100</v>
+        <v>774000</v>
       </c>
       <c r="F47" s="3">
-        <v>1576500</v>
+        <v>2091600</v>
       </c>
       <c r="G47" s="3">
-        <v>1662100</v>
+        <v>2385900</v>
       </c>
       <c r="H47" s="3">
-        <v>1195900</v>
+        <v>1840000</v>
       </c>
       <c r="I47" s="3">
-        <v>5277100</v>
+        <v>7050500</v>
       </c>
       <c r="J47" s="3">
-        <v>5114300</v>
+        <v>7128900</v>
       </c>
       <c r="K47" s="3">
         <v>4972400</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1890500</v>
+        <v>1760400</v>
       </c>
       <c r="E48" s="3">
-        <v>1800000</v>
+        <v>1907100</v>
       </c>
       <c r="F48" s="3">
-        <v>1747800</v>
+        <v>2027200</v>
       </c>
       <c r="G48" s="3">
-        <v>1814900</v>
+        <v>2311200</v>
       </c>
       <c r="H48" s="3">
-        <v>1853100</v>
+        <v>2425500</v>
       </c>
       <c r="I48" s="3">
-        <v>1777000</v>
+        <v>2258700</v>
       </c>
       <c r="J48" s="3">
-        <v>1775000</v>
+        <v>2354000</v>
       </c>
       <c r="K48" s="3">
         <v>1828300</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2928500</v>
+        <v>2726900</v>
       </c>
       <c r="E49" s="3">
-        <v>2601400</v>
+        <v>2756200</v>
       </c>
       <c r="F49" s="3">
-        <v>1842300</v>
+        <v>2136800</v>
       </c>
       <c r="G49" s="3">
-        <v>1601100</v>
+        <v>2039000</v>
       </c>
       <c r="H49" s="3">
-        <v>1646500</v>
+        <v>2155100</v>
       </c>
       <c r="I49" s="3">
-        <v>1560600</v>
+        <v>1983600</v>
       </c>
       <c r="J49" s="3">
-        <v>1541600</v>
+        <v>2044400</v>
       </c>
       <c r="K49" s="3">
         <v>2616300</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>919000</v>
+        <v>1537300</v>
       </c>
       <c r="E52" s="3">
-        <v>828600</v>
-      </c>
-      <c r="F52" s="3">
-        <v>803300</v>
-      </c>
-      <c r="G52" s="3">
-        <v>808700</v>
-      </c>
-      <c r="H52" s="3">
-        <v>711200</v>
-      </c>
-      <c r="I52" s="3">
-        <v>866300</v>
-      </c>
-      <c r="J52" s="3">
-        <v>891800</v>
+        <v>1351800</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K52" s="3">
         <v>828300</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>16231800</v>
+        <v>15114700</v>
       </c>
       <c r="E54" s="3">
-        <v>15264700</v>
+        <v>16173100</v>
       </c>
       <c r="F54" s="3">
-        <v>13158100</v>
+        <v>15261400</v>
       </c>
       <c r="G54" s="3">
-        <v>13403900</v>
+        <v>17069500</v>
       </c>
       <c r="H54" s="3">
-        <v>20360300</v>
+        <v>26650500</v>
       </c>
       <c r="I54" s="3">
-        <v>19348400</v>
+        <v>24592800</v>
       </c>
       <c r="J54" s="3">
-        <v>18751300</v>
+        <v>24867300</v>
       </c>
       <c r="K54" s="3">
         <v>18597600</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1678100</v>
+        <v>1562600</v>
       </c>
       <c r="E57" s="3">
-        <v>1548400</v>
+        <v>1640500</v>
       </c>
       <c r="F57" s="3">
-        <v>1259400</v>
+        <v>2211400</v>
       </c>
       <c r="G57" s="3">
-        <v>1428500</v>
+        <v>2596400</v>
       </c>
       <c r="H57" s="3">
-        <v>1274000</v>
+        <v>2286700</v>
       </c>
       <c r="I57" s="3">
-        <v>1478500</v>
+        <v>2763200</v>
       </c>
       <c r="J57" s="3">
-        <v>1380300</v>
+        <v>2831500</v>
       </c>
       <c r="K57" s="3">
         <v>1315800</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1243500</v>
+        <v>1157900</v>
       </c>
       <c r="E58" s="3">
-        <v>1306500</v>
+        <v>1384200</v>
       </c>
       <c r="F58" s="3">
-        <v>973100</v>
+        <v>1128700</v>
       </c>
       <c r="G58" s="3">
-        <v>768300</v>
+        <v>978400</v>
       </c>
       <c r="H58" s="3">
-        <v>558900</v>
+        <v>731600</v>
       </c>
       <c r="I58" s="3">
-        <v>1895400</v>
+        <v>2409100</v>
       </c>
       <c r="J58" s="3">
-        <v>1584700</v>
+        <v>2101500</v>
       </c>
       <c r="K58" s="3">
         <v>1549800</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3321300</v>
+        <v>3092700</v>
       </c>
       <c r="E59" s="3">
-        <v>3031800</v>
+        <v>3212300</v>
       </c>
       <c r="F59" s="3">
-        <v>2691000</v>
+        <v>2370500</v>
       </c>
       <c r="G59" s="3">
-        <v>2471600</v>
+        <v>2370300</v>
       </c>
       <c r="H59" s="3">
-        <v>9164300</v>
+        <v>2370300</v>
       </c>
       <c r="I59" s="3">
-        <v>2619900</v>
+        <v>2446100</v>
       </c>
       <c r="J59" s="3">
-        <v>2633500</v>
+        <v>2491400</v>
       </c>
       <c r="K59" s="3">
         <v>2573000</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>6242900</v>
+        <v>5813200</v>
       </c>
       <c r="E60" s="3">
-        <v>5886700</v>
+        <v>6237000</v>
       </c>
       <c r="F60" s="3">
-        <v>4923500</v>
+        <v>5710500</v>
       </c>
       <c r="G60" s="3">
-        <v>4668400</v>
+        <v>5945000</v>
       </c>
       <c r="H60" s="3">
-        <v>10997200</v>
+        <v>5388600</v>
       </c>
       <c r="I60" s="3">
-        <v>5993800</v>
+        <v>7618400</v>
       </c>
       <c r="J60" s="3">
-        <v>5598500</v>
+        <v>7424500</v>
       </c>
       <c r="K60" s="3">
         <v>5438700</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1739100</v>
+        <v>1619400</v>
       </c>
       <c r="E61" s="3">
-        <v>1727100</v>
+        <v>1829900</v>
       </c>
       <c r="F61" s="3">
-        <v>1175000</v>
+        <v>1362800</v>
       </c>
       <c r="G61" s="3">
-        <v>1323500</v>
+        <v>1685500</v>
       </c>
       <c r="H61" s="3">
-        <v>1185100</v>
+        <v>1551200</v>
       </c>
       <c r="I61" s="3">
-        <v>4731900</v>
+        <v>6014500</v>
       </c>
       <c r="J61" s="3">
-        <v>4676800</v>
+        <v>6202200</v>
       </c>
       <c r="K61" s="3">
         <v>4244800</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>687500</v>
+        <v>264400</v>
       </c>
       <c r="E62" s="3">
-        <v>848500</v>
+        <v>456300</v>
       </c>
       <c r="F62" s="3">
-        <v>628300</v>
+        <v>318200</v>
       </c>
       <c r="G62" s="3">
-        <v>852600</v>
+        <v>414900</v>
       </c>
       <c r="H62" s="3">
-        <v>1017500</v>
+        <v>9383400</v>
       </c>
       <c r="I62" s="3">
-        <v>1387900</v>
+        <v>791000</v>
       </c>
       <c r="J62" s="3">
-        <v>1455800</v>
+        <v>910200</v>
       </c>
       <c r="K62" s="3">
         <v>1386300</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>8856900</v>
+        <v>8072800</v>
       </c>
       <c r="E66" s="3">
-        <v>8650600</v>
+        <v>8965900</v>
       </c>
       <c r="F66" s="3">
-        <v>6753600</v>
+        <v>7802000</v>
       </c>
       <c r="G66" s="3">
-        <v>6870100</v>
+        <v>8716300</v>
       </c>
       <c r="H66" s="3">
-        <v>13825600</v>
+        <v>17277700</v>
       </c>
       <c r="I66" s="3">
-        <v>12727100</v>
+        <v>15397000</v>
       </c>
       <c r="J66" s="3">
-        <v>12293400</v>
+        <v>15557400</v>
       </c>
       <c r="K66" s="3">
         <v>11573800</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>3558100</v>
+        <v>3313200</v>
       </c>
       <c r="E72" s="3">
-        <v>3342100</v>
+        <v>3541000</v>
       </c>
       <c r="F72" s="3">
-        <v>3265000</v>
+        <v>3786900</v>
       </c>
       <c r="G72" s="3">
-        <v>3987200</v>
+        <v>5077600</v>
       </c>
       <c r="H72" s="3">
-        <v>4222600</v>
+        <v>5527100</v>
       </c>
       <c r="I72" s="3">
-        <v>4081600</v>
+        <v>5187900</v>
       </c>
       <c r="J72" s="3">
-        <v>3621800</v>
+        <v>4803100</v>
       </c>
       <c r="K72" s="3">
         <v>4431200</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>7374900</v>
+        <v>6867400</v>
       </c>
       <c r="E76" s="3">
-        <v>6614000</v>
+        <v>7007700</v>
       </c>
       <c r="F76" s="3">
-        <v>6404500</v>
+        <v>7428200</v>
       </c>
       <c r="G76" s="3">
-        <v>6533700</v>
+        <v>8320600</v>
       </c>
       <c r="H76" s="3">
-        <v>6534600</v>
+        <v>8553500</v>
       </c>
       <c r="I76" s="3">
-        <v>6621300</v>
+        <v>8416000</v>
       </c>
       <c r="J76" s="3">
-        <v>6457900</v>
+        <v>8564200</v>
       </c>
       <c r="K76" s="3">
         <v>7023800</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>313600</v>
+        <v>292100</v>
       </c>
       <c r="E81" s="3">
-        <v>386000</v>
+        <v>409000</v>
       </c>
       <c r="F81" s="3">
-        <v>215600</v>
+        <v>250100</v>
       </c>
       <c r="G81" s="3">
-        <v>-232400</v>
+        <v>-295900</v>
       </c>
       <c r="H81" s="3">
-        <v>280800</v>
+        <v>367500</v>
       </c>
       <c r="I81" s="3">
-        <v>351600</v>
+        <v>446900</v>
       </c>
       <c r="J81" s="3">
-        <v>-961100</v>
+        <v>-1274600</v>
       </c>
       <c r="K81" s="3">
         <v>23500</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>774100</v>
+        <v>502100</v>
       </c>
       <c r="E83" s="3">
-        <v>692000</v>
+        <v>548200</v>
       </c>
       <c r="F83" s="3">
-        <v>642400</v>
+        <v>745100</v>
       </c>
       <c r="G83" s="3">
-        <v>742800</v>
+        <v>945900</v>
       </c>
       <c r="H83" s="3">
-        <v>856900</v>
+        <v>1121600</v>
       </c>
       <c r="I83" s="3">
-        <v>669400</v>
+        <v>850900</v>
       </c>
       <c r="J83" s="3">
-        <v>769100</v>
+        <v>1020000</v>
       </c>
       <c r="K83" s="3">
         <v>720400</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>891900</v>
+        <v>830500</v>
       </c>
       <c r="E89" s="3">
-        <v>473600</v>
+        <v>501800</v>
       </c>
       <c r="F89" s="3">
-        <v>585500</v>
+        <v>679100</v>
       </c>
       <c r="G89" s="3">
-        <v>901400</v>
+        <v>1147900</v>
       </c>
       <c r="H89" s="3">
-        <v>828600</v>
+        <v>1084600</v>
       </c>
       <c r="I89" s="3">
-        <v>581800</v>
+        <v>739500</v>
       </c>
       <c r="J89" s="3">
-        <v>783000</v>
+        <v>1038400</v>
       </c>
       <c r="K89" s="3">
         <v>595100</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-378200</v>
+        <v>-352200</v>
       </c>
       <c r="E91" s="3">
-        <v>-322800</v>
+        <v>-342000</v>
       </c>
       <c r="F91" s="3">
-        <v>-265200</v>
+        <v>-307600</v>
       </c>
       <c r="G91" s="3">
-        <v>-299300</v>
+        <v>-381200</v>
       </c>
       <c r="H91" s="3">
-        <v>-614800</v>
+        <v>-804800</v>
       </c>
       <c r="I91" s="3">
-        <v>-514500</v>
+        <v>-653900</v>
       </c>
       <c r="J91" s="3">
-        <v>-513200</v>
+        <v>-680600</v>
       </c>
       <c r="K91" s="3">
         <v>-508500</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-694500</v>
+        <v>-646700</v>
       </c>
       <c r="E94" s="3">
-        <v>-951000</v>
+        <v>-1007600</v>
       </c>
       <c r="F94" s="3">
-        <v>-421400</v>
+        <v>-488800</v>
       </c>
       <c r="G94" s="3">
-        <v>-451300</v>
+        <v>-574700</v>
       </c>
       <c r="H94" s="3">
-        <v>-1168600</v>
+        <v>-1529600</v>
       </c>
       <c r="I94" s="3">
-        <v>-326100</v>
+        <v>-414500</v>
       </c>
       <c r="J94" s="3">
-        <v>-575600</v>
+        <v>-763400</v>
       </c>
       <c r="K94" s="3">
         <v>-719300</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-151400</v>
+        <v>140900</v>
       </c>
       <c r="E96" s="3">
-        <v>-132300</v>
+        <v>140200</v>
       </c>
       <c r="F96" s="3">
-        <v>-99800</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>-105400</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-133800</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-90100</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>-102900</v>
+        <v>0</v>
       </c>
       <c r="K96" s="3">
         <v>-195400</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-588700</v>
+        <v>-548200</v>
       </c>
       <c r="E100" s="3">
-        <v>251700</v>
+        <v>266700</v>
       </c>
       <c r="F100" s="3">
-        <v>-935000</v>
+        <v>-1084400</v>
       </c>
       <c r="G100" s="3">
-        <v>-29000</v>
+        <v>-36900</v>
       </c>
       <c r="H100" s="3">
-        <v>537900</v>
+        <v>704000</v>
       </c>
       <c r="I100" s="3">
-        <v>301200</v>
+        <v>382900</v>
       </c>
       <c r="J100" s="3">
-        <v>45500</v>
+        <v>60300</v>
       </c>
       <c r="K100" s="3">
         <v>-134300</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>98600</v>
+        <v>91800</v>
       </c>
       <c r="E101" s="3">
-        <v>61400</v>
+        <v>65000</v>
       </c>
       <c r="F101" s="3">
-        <v>87000</v>
+        <v>100900</v>
       </c>
       <c r="G101" s="3">
-        <v>52100</v>
+        <v>66300</v>
       </c>
       <c r="H101" s="3">
-        <v>-30400</v>
+        <v>-39800</v>
       </c>
       <c r="I101" s="3">
-        <v>7700</v>
+        <v>9800</v>
       </c>
       <c r="J101" s="3">
-        <v>-10500</v>
+        <v>-13900</v>
       </c>
       <c r="K101" s="3">
         <v>-18700</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-292800</v>
+        <v>-272700</v>
       </c>
       <c r="E102" s="3">
-        <v>-164300</v>
+        <v>-174000</v>
       </c>
       <c r="F102" s="3">
-        <v>-683900</v>
+        <v>-793200</v>
       </c>
       <c r="G102" s="3">
-        <v>473300</v>
+        <v>602700</v>
       </c>
       <c r="H102" s="3">
-        <v>167500</v>
+        <v>219200</v>
       </c>
       <c r="I102" s="3">
-        <v>564700</v>
+        <v>717700</v>
       </c>
       <c r="J102" s="3">
-        <v>242400</v>
+        <v>321400</v>
       </c>
       <c r="K102" s="3">
         <v>-277100</v>

--- a/AAII_Financials/Yearly/RICOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RICOY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
   <si>
     <t>RICOY</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44651</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44286</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43921</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43555</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43190</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42825</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42460</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42094</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41729</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41364</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40999</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>16880900</v>
+      </c>
+      <c r="E8" s="3">
         <v>15530000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>16054400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>14481800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>15208700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>18666800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>18168300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>19428100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13674800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>16236400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>18351500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>20112600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>17143700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>17207400</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>11080400</v>
+      </c>
+      <c r="E9" s="3">
         <v>10108000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10447000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>9354200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>10034100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>11960800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>11247600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>11980200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>8359400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>9753900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10615500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>12113800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>20836800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10403700</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>5800500</v>
+      </c>
+      <c r="E10" s="3">
         <v>5422000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5607500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5127600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5174600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>6706000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6920700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7447900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5315400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6482400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>7736000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>7998700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-3693100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>6803700</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,53 +886,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="3">
         <v>692100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>688600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>796500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>716000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>819900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>848500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>885000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>676600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>750000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>838400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>864400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1831000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1076000</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -963,99 +979,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E14" s="3">
         <v>-9600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-100600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-112800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>21400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-57500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-178400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1266000</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N14" s="3">
         <v>8600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>103700</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>293800</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>760100</v>
+      </c>
+      <c r="E15" s="3">
         <v>401600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>426800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>414500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>492100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>495700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>224400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>377500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>271500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>273000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>318200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>339900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>321800</v>
       </c>
-      <c r="P15" s="3" t="s">
+      <c r="Q15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>16445900</v>
+      </c>
+      <c r="E17" s="3">
         <v>15129500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>15562700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>14274200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>15610400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>17989700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>17563000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>19250300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>13446400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15484500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>17364000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>19010200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>16475100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>17416100</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>435000</v>
+      </c>
+      <c r="E18" s="3">
         <v>400500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>491700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>207600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-401600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>677100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>605200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>177800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>228400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>751900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>987500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1102400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>668600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-208600</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,233 +1211,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-38300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-39900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-31300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-54600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-60300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>18000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>9300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>54500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>24400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>31100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>47400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>84400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-17000</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1233300</v>
+      </c>
+      <c r="E21" s="3">
         <v>842000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>949800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>676700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>150700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1154800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>820300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>500800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>976400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1533000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1949200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2127000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1626800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>599200</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>70300</v>
+      </c>
+      <c r="E22" s="3">
         <v>36400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>45200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>26800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>27500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>53600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>53800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>63300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>50900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>48100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>60700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>68300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>134100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>63100</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>467900</v>
+      </c>
+      <c r="E23" s="3">
         <v>450900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>611600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>365500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-371000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>705300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>757700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1169300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>201900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>703300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>957900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1081500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>618900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-288700</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>160200</v>
+      </c>
+      <c r="E24" s="3">
         <v>158400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>193100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>113300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-75600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>292500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>258000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>51400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>138300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>208600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>329200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>362800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>220600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>74300</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>307700</v>
+      </c>
+      <c r="E26" s="3">
         <v>292500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>418600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>252200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-295300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>412800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>499700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1220600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>63600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>494700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>628700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>718600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>398300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-363000</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>305200</v>
+      </c>
+      <c r="E27" s="3">
         <v>292100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>409000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>250100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-295900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>367500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>446900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1274600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>23500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>462900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>584800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>667000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>309500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-402800</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1610,8 +1670,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>10</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>10</v>
@@ -1628,9 +1688,12 @@
       <c r="P29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>38300</v>
+      </c>
+      <c r="E32" s="3">
         <v>39900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>31300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>54600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>60300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-18000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-9300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-54500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-24400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-31100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-47400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-84400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>17000</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>305200</v>
+      </c>
+      <c r="E33" s="3">
         <v>292100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>409000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>250100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-295900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>367500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>446900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1274600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>23500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>462900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>584800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>667000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>309500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-402800</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>305200</v>
+      </c>
+      <c r="E35" s="3">
         <v>292100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>409000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>250100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-295900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>367500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>446900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1274600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>23500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>462900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>584800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>667000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>309500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-402800</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44651</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44286</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43921</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43555</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43190</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42825</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42460</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42094</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41729</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41364</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40999</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,65 +2072,69 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1284100</v>
+      </c>
+      <c r="E41" s="3">
         <v>1170500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1669200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1979600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3029400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2443100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2167400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1512500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>852100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1238600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1182700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1320000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2187600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1412100</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>1800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1600</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -2056,344 +2145,368 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>526500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1922500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2001800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2218300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2287100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2103200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>22200</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3613600</v>
+      </c>
+      <c r="E43" s="3">
         <v>3557300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3584000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3270500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3545500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3650300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5458000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5552900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3817000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4146900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4721600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9979400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>8964400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6209800</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1996000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1987300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2364800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1915100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1736100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1870300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1874800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1699400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1365200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1522100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1914800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1778600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3563900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1762900</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1209500</v>
+      </c>
+      <c r="E45" s="3">
         <v>1238500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1221700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1172100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1261700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>11609800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3041600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3212600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>395500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>448600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>338300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>314300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3011200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>595700</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8103300</v>
+      </c>
+      <c r="E46" s="3">
         <v>7955400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8841200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8337200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9572800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>19573500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12541800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>12503900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8352300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9358000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>10375700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10689700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9593000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>10002800</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2473100</v>
+      </c>
+      <c r="E47" s="3">
         <v>694600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>774000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2091600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2385900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1840000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>7050500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>7128900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4972400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5058200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5633900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>5612200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>5473000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4645800</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1826500</v>
+      </c>
+      <c r="E48" s="3">
         <v>1760400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1907100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2027200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2311200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2425500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2258700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2354000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1828300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2032600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2359500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2894700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5065200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2427500</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2890100</v>
+      </c>
+      <c r="E49" s="3">
         <v>2726900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2756200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2136800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2039000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2155100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1983600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2044400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2616300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3041700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3717000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3658100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4520200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2785800</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,20 +2597,23 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E52" s="3">
         <v>1537300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1351800</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -2508,27 +2627,30 @@
       <c r="J52" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L52" s="3">
         <v>828300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>916500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1202500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1345400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6546100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>833900</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15740600</v>
+      </c>
+      <c r="E54" s="3">
         <v>15114700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>16173100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>15261400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>17069500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>26650500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>24592800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>24867300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>18597600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>20407000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>23288700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>23785000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>21735700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>20695800</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,278 +2784,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2221700</v>
+      </c>
+      <c r="E57" s="3">
         <v>1562600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1640500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2211400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2596400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2286700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2763200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2831500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1315800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1457300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2362700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1965300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3862300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2175500</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1137500</v>
+      </c>
+      <c r="E58" s="3">
         <v>1157900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1384200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1128700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>978400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>731600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2409100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2101500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1549800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1916500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1894200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2489400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4128200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2061000</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2382700</v>
+      </c>
+      <c r="E59" s="3">
         <v>3092700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3212300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2370500</v>
-      </c>
-      <c r="G59" s="3">
-        <v>2370300</v>
       </c>
       <c r="H59" s="3">
         <v>2370300</v>
       </c>
       <c r="I59" s="3">
+        <v>2370300</v>
+      </c>
+      <c r="J59" s="3">
         <v>2446100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2491400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2573000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2556600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2329400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3200300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4746300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1847600</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5741900</v>
+      </c>
+      <c r="E60" s="3">
         <v>5813200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6237000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5710500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5945000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5388600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7618400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7424500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5438700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5930500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6586300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7654900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6370500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6084100</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2309700</v>
+      </c>
+      <c r="E61" s="3">
         <v>1619400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1829900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1362800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1685500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1551200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6014500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6202200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4244800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4351500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4849400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4143900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4314000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4749900</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>251200</v>
+      </c>
+      <c r="E62" s="3">
         <v>264400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>456300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>318200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>414900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9383400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>791000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>910200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1386300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1688900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2006600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1961500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4245400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1915400</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8697100</v>
+      </c>
+      <c r="E66" s="3">
         <v>8072800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8965900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7802000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8716300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>17277700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>15397000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>15557400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11573800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>12485100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14040700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14355600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13430100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13258600</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3152600</v>
+      </c>
+      <c r="E72" s="3">
         <v>3313200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3541000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3786900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>5077600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5527100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5187900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4803100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4431200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4986400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5514400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5728100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>12094900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6712600</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6878900</v>
+      </c>
+      <c r="E76" s="3">
         <v>6867400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7007700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7428200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8320600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8553500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8416000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8564200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7023800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7921900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9247900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9429400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8305600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7437200</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44651</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44286</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43921</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43555</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43190</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42825</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42460</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42094</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41729</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41364</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40999</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>305200</v>
+      </c>
+      <c r="E81" s="3">
         <v>292100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>409000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>250100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-295900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>367500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>446900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1274600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>23500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>462900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>584800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>667000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>309500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-402800</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>760100</v>
+      </c>
+      <c r="E83" s="3">
         <v>502100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>548200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>745100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>945900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1121600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>850900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1020000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>720400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>789100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>919800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>973100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>871900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>823900</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>914000</v>
+      </c>
+      <c r="E89" s="3">
         <v>830500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>501800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>679100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1147900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1084600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>739500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1038400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>595100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>734000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>874700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1345500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1248200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>101300</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-327100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-352200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-342000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-307600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-381200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-804800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-653900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-680600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-508500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-615800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-648100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-668600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1507600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-662400</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-530000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-646700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1007600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-488800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-574700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1529600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-414500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-763400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-719300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-765400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1223700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1126100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1106600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1016500</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,20 +4453,21 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>140900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>140200</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
@@ -4248,26 +4481,29 @@
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-195400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-183800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-207200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-219200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-138400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-216400</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-304300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-548200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>266700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1084400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-36900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>704000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>382900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>60300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-134300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>313600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>255400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-84600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-562100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>793900</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E101" s="3">
         <v>91800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>65000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>100900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>66300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-39800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>9800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-13900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-18700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-62900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>73800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>75800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>64600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-23500</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>81600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-272700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-174000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-793200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>602700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>219200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>717700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>321400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-277100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>219200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-19800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>210600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-356000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-144700</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/RICOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RICOY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
   <si>
     <t>RICOY</t>
   </si>
@@ -892,8 +892,8 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>10</v>
+      <c r="D12" s="3">
+        <v>635600</v>
       </c>
       <c r="E12" s="3">
         <v>692100</v>
@@ -989,10 +989,10 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>8800</v>
+        <v>164800</v>
       </c>
       <c r="E14" s="3">
-        <v>-9600</v>
+        <v>-1300</v>
       </c>
       <c r="F14" s="3">
         <v>-100600</v>
@@ -1037,7 +1037,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>760100</v>
+        <v>423600</v>
       </c>
       <c r="E15" s="3">
         <v>401600</v>
@@ -1102,10 +1102,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>16445900</v>
+        <v>16289800</v>
       </c>
       <c r="E17" s="3">
-        <v>15129500</v>
+        <v>15121300</v>
       </c>
       <c r="F17" s="3">
         <v>15562700</v>
@@ -1150,10 +1150,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>435000</v>
+        <v>591100</v>
       </c>
       <c r="E18" s="3">
-        <v>400500</v>
+        <v>408700</v>
       </c>
       <c r="F18" s="3">
         <v>491700</v>
@@ -1218,7 +1218,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-38300</v>
+        <v>-52600</v>
       </c>
       <c r="E20" s="3">
         <v>-39900</v>
@@ -1266,10 +1266,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1233300</v>
+        <v>1067300</v>
       </c>
       <c r="E21" s="3">
-        <v>842000</v>
+        <v>850200</v>
       </c>
       <c r="F21" s="3">
         <v>949800</v>
@@ -1314,7 +1314,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>70300</v>
+        <v>47200</v>
       </c>
       <c r="E22" s="3">
         <v>36400</v>
@@ -1794,7 +1794,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>38300</v>
+        <v>52600</v>
       </c>
       <c r="E32" s="3">
         <v>39900</v>
@@ -2079,7 +2079,7 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1284100</v>
+        <v>1273200</v>
       </c>
       <c r="E41" s="3">
         <v>1170500</v>
@@ -2127,7 +2127,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>10900</v>
       </c>
       <c r="E42" s="3">
         <v>1800</v>
@@ -2367,7 +2367,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2473100</v>
+        <v>747200</v>
       </c>
       <c r="E47" s="3">
         <v>694600</v>
@@ -2606,8 +2606,8 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>10</v>
+      <c r="D52" s="3">
+        <v>1725900</v>
       </c>
       <c r="E52" s="3">
         <v>1537300</v>
@@ -2791,7 +2791,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2221700</v>
+        <v>1705400</v>
       </c>
       <c r="E57" s="3">
         <v>1562600</v>
@@ -2887,7 +2887,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2382700</v>
+        <v>2899000</v>
       </c>
       <c r="E59" s="3">
         <v>3092700</v>
@@ -3892,7 +3892,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>760100</v>
+        <v>522200</v>
       </c>
       <c r="E83" s="3">
         <v>502100</v>
@@ -4460,7 +4460,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>146900</v>
       </c>
       <c r="E96" s="3">
         <v>140900</v>
